--- a/Result/checksun_type/電網營造.xlsx
+++ b/Result/checksun_type/電網營造.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI34"/>
+  <dimension ref="A1:CI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>617.266</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10385,107 +10385,107 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-75.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2025-11-05 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2025-11-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-09-10 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2025-09-11 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>605.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -10501,140 +10501,140 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>745.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>695.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>631.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>633.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>4929548641.36344</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>453518166.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>696124492.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>2883970531.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>2126707687.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>29518563.01117429</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BC24" t="n">
-        <v>-630160054.09</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>772.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -10739,27 +10739,27 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
+          <t>電機機械右下上市</t>
         </is>
       </c>
       <c r="CC24" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>730.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -10773,4316 +10773,6 @@
         </is>
       </c>
       <c r="CI24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>-3.17</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1116.653</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>722.0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-80.90</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>-8.03</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>-3.99</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>9.29</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>9.44</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>752.0</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>688.05</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>628.72</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>632.04</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>42.23</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>40.46</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr">
-        <is>
-          <t>-49.89</t>
-        </is>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>4929548641.36344</t>
-        </is>
-      </c>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>811169006.0</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>779349653.2</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>4079717323.9</t>
-        </is>
-      </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2168937186.34</t>
-        </is>
-      </c>
-      <c r="BA25" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>149460129.7576182</t>
-        </is>
-      </c>
-      <c r="BC25" t="n">
-        <v>-567096178.3200001</v>
-      </c>
-      <c r="BD25" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BE25" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BF25" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
-        <is>
-          <t>-6.48</t>
-        </is>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BI25" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ25" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK25" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL25" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BM25" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="BN25" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="BO25" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="BP25" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ25" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR25" t="inlineStr">
-        <is>
-          <t>26.03</t>
-        </is>
-      </c>
-      <c r="BS25" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="BT25" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="BU25" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="BV25" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="BW25" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="BX25" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BY25" t="inlineStr">
-        <is>
-          <t>233119</t>
-        </is>
-      </c>
-      <c r="BZ25" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA25" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CC25" t="inlineStr">
-        <is>
-          <t>725.0</t>
-        </is>
-      </c>
-      <c r="CD25" t="inlineStr">
-        <is>
-          <t>736.0</t>
-        </is>
-      </c>
-      <c r="CE25" t="inlineStr">
-        <is>
-          <t>722.0</t>
-        </is>
-      </c>
-      <c r="CF25" t="inlineStr">
-        <is>
-          <t>722.0</t>
-        </is>
-      </c>
-      <c r="CG25" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CH25" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CI25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>-2.6</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1008.586</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>745.0</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-82.40</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>-5.10</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>-2.14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>49.94</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>-1.56</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>8.78</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>756.8</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>681.7</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>626.7</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>630.91</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>15.69</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>46.30</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>40.02</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr">
-        <is>
-          <t>-50.44</t>
-        </is>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV26" t="inlineStr">
-        <is>
-          <t>4929548641.36344</t>
-        </is>
-      </c>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>757270421.0</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>855936440.6</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>4864530439.2</t>
-        </is>
-      </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>2227082877.5</t>
-        </is>
-      </c>
-      <c r="BA26" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB26" t="inlineStr">
-        <is>
-          <t>279743094.8631054</t>
-        </is>
-      </c>
-      <c r="BC26" t="n">
-        <v>-495071225.14</v>
-      </c>
-      <c r="BD26" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BE26" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BF26" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BG26" t="inlineStr">
-        <is>
-          <t>-3.50</t>
-        </is>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BI26" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ26" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK26" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL26" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BM26" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="BN26" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="BO26" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="BP26" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ26" t="inlineStr">
-        <is>
-          <t>價跌量-</t>
-        </is>
-      </c>
-      <c r="BR26" t="inlineStr">
-        <is>
-          <t>26.86</t>
-        </is>
-      </c>
-      <c r="BS26" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="BT26" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="BU26" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="BV26" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="BW26" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="BX26" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BY26" t="inlineStr">
-        <is>
-          <t>233119</t>
-        </is>
-      </c>
-      <c r="BZ26" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA26" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CB26" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CC26" t="inlineStr">
-        <is>
-          <t>769.0</t>
-        </is>
-      </c>
-      <c r="CD26" t="inlineStr">
-        <is>
-          <t>769.0</t>
-        </is>
-      </c>
-      <c r="CE26" t="inlineStr">
-        <is>
-          <t>737.0</t>
-        </is>
-      </c>
-      <c r="CF26" t="inlineStr">
-        <is>
-          <t>745.0</t>
-        </is>
-      </c>
-      <c r="CG26" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CH26" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CI26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>711.087</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>765.0</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-3.66</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>-81.30</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>70.42</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>80.35</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>760.8</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>624.74</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>629.5</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>26.07</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>48.47</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>38.45</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>-52.39</t>
-        </is>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV27" t="inlineStr">
-        <is>
-          <t>4929548641.36344</t>
-        </is>
-      </c>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>543477829.0</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>1032473983.6</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>5522062366.6</t>
-        </is>
-      </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>2292721646.52</t>
-        </is>
-      </c>
-      <c r="BA27" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB27" t="inlineStr">
-        <is>
-          <t>420618425.772247</t>
-        </is>
-      </c>
-      <c r="BC27" t="n">
-        <v>-368722471.3</v>
-      </c>
-      <c r="BD27" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BE27" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BF27" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BG27" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BI27" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ27" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK27" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL27" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BM27" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="BN27" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="BO27" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="BP27" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ27" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR27" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
-      </c>
-      <c r="BS27" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="BT27" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="BU27" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="BV27" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="BW27" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="BX27" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BY27" t="inlineStr">
-        <is>
-          <t>233119</t>
-        </is>
-      </c>
-      <c r="BZ27" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA27" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CB27" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CC27" t="inlineStr">
-        <is>
-          <t>765.0</t>
-        </is>
-      </c>
-      <c r="CD27" t="inlineStr">
-        <is>
-          <t>770.0</t>
-        </is>
-      </c>
-      <c r="CE27" t="inlineStr">
-        <is>
-          <t>759.0</t>
-        </is>
-      </c>
-      <c r="CF27" t="inlineStr">
-        <is>
-          <t>765.0</t>
-        </is>
-      </c>
-      <c r="CG27" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CH27" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CI27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1193.09</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>758.0</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-2.71</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-57.71</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>-3.44</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>-2.90</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>79.41</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>82.88</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>15.48</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>6.51</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>764.8</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>662.3</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>621.8</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>627.64</t>
-        </is>
-      </c>
-      <c r="AP28" t="inlineStr">
-        <is>
-          <t>34.94</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>48.50</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>35.94</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT28" t="inlineStr">
-        <is>
-          <t>-55.49</t>
-        </is>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV28" t="inlineStr">
-        <is>
-          <t>4929548641.36344</t>
-        </is>
-      </c>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>915187042.0</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>2404829140.4</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>5686609711.2</t>
-        </is>
-      </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>2312774767.92</t>
-        </is>
-      </c>
-      <c r="BA28" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t>564134952.5119295</t>
-        </is>
-      </c>
-      <c r="BC28" t="n">
-        <v>-152149242.69</v>
-      </c>
-      <c r="BD28" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BE28" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BF28" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BG28" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BI28" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ28" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK28" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL28" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BM28" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="BN28" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="BO28" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="BP28" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ28" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR28" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
-      <c r="BS28" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="BT28" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="BU28" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="BV28" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="BW28" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="BX28" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BY28" t="inlineStr">
-        <is>
-          <t>233119</t>
-        </is>
-      </c>
-      <c r="BZ28" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA28" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CB28" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CC28" t="inlineStr">
-        <is>
-          <t>775.0</t>
-        </is>
-      </c>
-      <c r="CD28" t="inlineStr">
-        <is>
-          <t>780.0</t>
-        </is>
-      </c>
-      <c r="CE28" t="inlineStr">
-        <is>
-          <t>758.0</t>
-        </is>
-      </c>
-      <c r="CF28" t="inlineStr">
-        <is>
-          <t>758.0</t>
-        </is>
-      </c>
-      <c r="CG28" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CH28" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CI28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1144.535</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>770.0</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>-4.34</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>-15.19</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>4.34</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>91.21</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>86.14</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>17.70</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>5.32</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>767.6</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>652.15</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>619.2</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>625.75</t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>48.00</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>48.55</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>32.80</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT29" t="inlineStr">
-        <is>
-          <t>-59.38</t>
-        </is>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV29" t="inlineStr">
-        <is>
-          <t>4929548641.36344</t>
-        </is>
-      </c>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>869643968.0</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>5071816570.6</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>5980378748.8</t>
-        </is>
-      </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>2324099002.48</t>
-        </is>
-      </c>
-      <c r="BA29" t="inlineStr">
-        <is>
-          <t>-908562178</t>
-        </is>
-      </c>
-      <c r="BB29" t="inlineStr">
-        <is>
-          <t>694368442.54881</t>
-        </is>
-      </c>
-      <c r="BC29" t="n">
-        <v>122848998.31</v>
-      </c>
-      <c r="BD29" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BE29" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BI29" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ29" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK29" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL29" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BM29" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="BN29" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="BO29" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="BP29" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ29" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BR29" t="inlineStr">
-        <is>
-          <t>27.76</t>
-        </is>
-      </c>
-      <c r="BS29" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="BT29" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="BU29" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="BV29" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="BW29" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="BX29" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BY29" t="inlineStr">
-        <is>
-          <t>233119</t>
-        </is>
-      </c>
-      <c r="BZ29" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA29" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CB29" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CC29" t="inlineStr">
-        <is>
-          <t>765.0</t>
-        </is>
-      </c>
-      <c r="CD29" t="inlineStr">
-        <is>
-          <t>770.0</t>
-        </is>
-      </c>
-      <c r="CE29" t="inlineStr">
-        <is>
-          <t>750.0</t>
-        </is>
-      </c>
-      <c r="CF29" t="inlineStr">
-        <is>
-          <t>770.0</t>
-        </is>
-      </c>
-      <c r="CG29" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CH29" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CI29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>-2.52</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1587.408</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>746.0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>-4.97</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>5.66</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>-3.35</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>78.02</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>88.9</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>-3.22</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>20.18</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>4.12</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>-1.29</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>770.8</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>641.35</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>616.0</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>624.02</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr">
-        <is>
-          <t>61.71</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>46.68</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>28.87</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr">
-        <is>
-          <t>-64.25</t>
-        </is>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV30" t="inlineStr">
-        <is>
-          <t>4929548641.36344</t>
-        </is>
-      </c>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>1194102943.0</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>7380084994.6</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>5968914067.6</t>
-        </is>
-      </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>2329253341.64</t>
-        </is>
-      </c>
-      <c r="BA30" t="inlineStr">
-        <is>
-          <t>1411170927</t>
-        </is>
-      </c>
-      <c r="BB30" t="inlineStr">
-        <is>
-          <t>798281068.7748979</t>
-        </is>
-      </c>
-      <c r="BC30" t="n">
-        <v>516195779.15</v>
-      </c>
-      <c r="BD30" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BE30" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BF30" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr">
-        <is>
-          <t>-3.37</t>
-        </is>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BI30" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ30" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK30" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL30" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BM30" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="BN30" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="BO30" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="BP30" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ30" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BR30" t="inlineStr">
-        <is>
-          <t>26.89</t>
-        </is>
-      </c>
-      <c r="BS30" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="BT30" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="BU30" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="BV30" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="BW30" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="BX30" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BY30" t="inlineStr">
-        <is>
-          <t>233119</t>
-        </is>
-      </c>
-      <c r="BZ30" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA30" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CB30" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CC30" t="inlineStr">
-        <is>
-          <t>755.0</t>
-        </is>
-      </c>
-      <c r="CD30" t="inlineStr">
-        <is>
-          <t>774.0</t>
-        </is>
-      </c>
-      <c r="CE30" t="inlineStr">
-        <is>
-          <t>743.0</t>
-        </is>
-      </c>
-      <c r="CF30" t="inlineStr">
-        <is>
-          <t>746.0</t>
-        </is>
-      </c>
-      <c r="CG30" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CH30" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CI30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2119.821</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>765.0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>-3.66</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>49.26</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>7.56</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>-2.61</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>89.18</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>93.92</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>20.88</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>-1.46</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>764.6</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>632.55</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>613.28</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>622.34</t>
-        </is>
-      </c>
-      <c r="AP31" t="inlineStr">
-        <is>
-          <t>88.66</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>46.06</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr">
-        <is>
-          <t>-69.77</t>
-        </is>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV31" t="inlineStr">
-        <is>
-          <t>4929548641.36344</t>
-        </is>
-      </c>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>1639958136.0</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>8873124437.8</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>5944629753.8</t>
-        </is>
-      </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2333052998.56</t>
-        </is>
-      </c>
-      <c r="BA31" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB31" t="inlineStr">
-        <is>
-          <t>849569303.2528446</t>
-        </is>
-      </c>
-      <c r="BC31" t="n">
-        <v>1024920726.63</v>
-      </c>
-      <c r="BD31" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BE31" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BF31" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BI31" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ31" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK31" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL31" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BM31" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="BN31" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="BO31" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="BP31" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ31" t="inlineStr">
-        <is>
-          <t>價跌量縮</t>
-        </is>
-      </c>
-      <c r="BR31" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
-      </c>
-      <c r="BS31" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="BT31" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="BU31" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="BV31" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="BW31" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="BX31" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BY31" t="inlineStr">
-        <is>
-          <t>233119</t>
-        </is>
-      </c>
-      <c r="BZ31" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA31" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CB31" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CC31" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="CD31" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="CE31" t="inlineStr">
-        <is>
-          <t>765.0</t>
-        </is>
-      </c>
-      <c r="CF31" t="inlineStr">
-        <is>
-          <t>765.0</t>
-        </is>
-      </c>
-      <c r="CG31" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CH31" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CI31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>9688.689</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-6.37</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>70.54</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>6.37</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>34.55</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>5.41</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>97.52</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>5.85</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>741.6</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>623.0</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>609.92</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>620.01</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>124.51</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>42.66</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>19.00</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>-76.47</t>
-        </is>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV32" t="inlineStr">
-        <is>
-          <t>4929548641.36344</t>
-        </is>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>7405253613.0</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>10011650749.6</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>5870589709.3</t>
-        </is>
-      </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2337679186.88</t>
-        </is>
-      </c>
-      <c r="BA32" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB32" t="inlineStr">
-        <is>
-          <t>817687226.2755579</t>
-        </is>
-      </c>
-      <c r="BC32" t="n">
-        <v>1667296140.69</v>
-      </c>
-      <c r="BD32" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BE32" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BI32" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ32" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK32" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL32" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BM32" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="BN32" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="BO32" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="BP32" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ32" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR32" t="inlineStr">
-        <is>
-          <t>28.30</t>
-        </is>
-      </c>
-      <c r="BS32" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="BT32" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="BU32" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="BV32" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="BW32" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="BX32" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BY32" t="inlineStr">
-        <is>
-          <t>233119</t>
-        </is>
-      </c>
-      <c r="BZ32" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA32" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CB32" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CC32" t="inlineStr">
-        <is>
-          <t>748.0</t>
-        </is>
-      </c>
-      <c r="CD32" t="inlineStr">
-        <is>
-          <t>788.0</t>
-        </is>
-      </c>
-      <c r="CE32" t="inlineStr">
-        <is>
-          <t>742.0</t>
-        </is>
-      </c>
-      <c r="CF32" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="CG32" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CH32" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CI32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>18118.77</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-4.61</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>69.40</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>4.61</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>64.61</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>93.07</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>97.69</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>9.44</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>15.20</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>705.4</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>612.35</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>606.42</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>617.41</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>172.56</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>35.67</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>-83.79</t>
-        </is>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV33" t="inlineStr">
-        <is>
-          <t>4929548641.36344</t>
-        </is>
-      </c>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>14250124193.0</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>8968390282.0</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>5294074253.1</t>
-        </is>
-      </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2221550552.1</t>
-        </is>
-      </c>
-      <c r="BA33" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB33" t="inlineStr">
-        <is>
-          <t>663212878.2008342</t>
-        </is>
-      </c>
-      <c r="BC33" t="n">
-        <v>1907718783.21</v>
-      </c>
-      <c r="BD33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE33" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BF33" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BI33" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ33" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK33" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL33" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BM33" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="BN33" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="BO33" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="BP33" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ33" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR33" t="inlineStr">
-        <is>
-          <t>27.83</t>
-        </is>
-      </c>
-      <c r="BS33" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="BT33" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="BU33" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="BV33" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="BW33" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="BX33" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BY33" t="inlineStr">
-        <is>
-          <t>233119</t>
-        </is>
-      </c>
-      <c r="BZ33" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA33" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CB33" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CC33" t="inlineStr">
-        <is>
-          <t>800.0</t>
-        </is>
-      </c>
-      <c r="CD33" t="inlineStr">
-        <is>
-          <t>816.0</t>
-        </is>
-      </c>
-      <c r="CE33" t="inlineStr">
-        <is>
-          <t>763.0</t>
-        </is>
-      </c>
-      <c r="CF33" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="CG33" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CH33" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CI33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>9.45</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>16158.888</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>786.0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-6.5</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>70.78</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>624.0</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>605.0</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>6.22</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>12.08</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>674.6</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>601.9</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>603.2</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>614.95</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>270.23</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>27.55</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>7.44</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>-90.78</t>
-        </is>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>2025/10/16</t>
-        </is>
-      </c>
-      <c r="AV34" t="inlineStr">
-        <is>
-          <t>4929548641.36344</t>
-        </is>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>12410986088.0</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>6888940927.0</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>4033826236.5</t>
-        </is>
-      </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1975526023.72</t>
-        </is>
-      </c>
-      <c r="BA34" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>436939077.2900687</t>
-        </is>
-      </c>
-      <c r="BC34" t="n">
-        <v>1449667896.7</v>
-      </c>
-      <c r="BD34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE34" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BI34" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BJ34" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BK34" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL34" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BM34" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="BN34" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="BO34" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="BP34" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BQ34" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR34" t="inlineStr">
-        <is>
-          <t>28.33</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="BT34" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="BU34" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="BV34" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="BW34" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="BX34" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
-      </c>
-      <c r="BY34" t="inlineStr">
-        <is>
-          <t>233119</t>
-        </is>
-      </c>
-      <c r="BZ34" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA34" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CB34" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CC34" t="inlineStr">
-        <is>
-          <t>751.0</t>
-        </is>
-      </c>
-      <c r="CD34" t="inlineStr">
-        <is>
-          <t>786.0</t>
-        </is>
-      </c>
-      <c r="CE34" t="inlineStr">
-        <is>
-          <t>740.0</t>
-        </is>
-      </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>786.0</t>
-        </is>
-      </c>
-      <c r="CG34" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CH34" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CI34" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/電網營造.xlsx
+++ b/Result/checksun_type/電網營造.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>99.47999999999999</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>102.82</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>105</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>103180579.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>116147614.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>116147614.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>176548720.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>201428975.56</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>201428975.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-25860202.92993152</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>103180579</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>103180579.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>98.94</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>103.24</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>105.06</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>103.24</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>105.06</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>78066930.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>134482037.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>134482037.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>193869170.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>205225010.12</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>205225010.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-24317788.82020301</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>78066930</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>78066930.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>98.72</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>103.7</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>105.23</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>105.23</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>136094275.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>162561404.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>162561404.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>195664628.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>209197245.52</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>209197245.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-18555099.52701217</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>136094275</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>136094275.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>98.9</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>104.3</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>105.44</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>105.44</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>116900919.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>222301963.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>222301963.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>191158060.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>220229469.28</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>220229469.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-15877219.6607748</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>116900919</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>116900919.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>99.6</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>104.8</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>105.6</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>146495369.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>240594220.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>240594220.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>198554746.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>221461486.3</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>221461486.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-9428202.435408056</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>146495369</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>146495369.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>100.4</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>105.28</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>105.69</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>105.28</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>105.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>194852695.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>236949826.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>236949826.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>211794368.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>221171326.8</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>221171326.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-3049433.097905278</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>194852695</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>194852695.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>101.84</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>105.84</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>105.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>218463765.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>253256304.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>253256304</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>212975569.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>219688213.02</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>219688213.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>990860.7805953324</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>218463765</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>102.86</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>106.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>106</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>434797068.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>228767852.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>230869656.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>217695178.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>4197563.793432087</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>434797068</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>434797068.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>103.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>106.6</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>106.11</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>106.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>208362204.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>160014158.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>160014158.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>237292886.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>210329621.68</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>210329621.68</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-14549913.0737094</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>208362204</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>106.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>128273399.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>156515273.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>280273763.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>208482988.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-16551504.84556478</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>128273399</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>128273399.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>106.85</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>106.24</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>276385084.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>186638909.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>186638909.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>285043227.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>208948816.74</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>208948816.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-10238853.09658802</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>276385084</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>276385084.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>67.44000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>62.95</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>57.54</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>57.54</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>68305837.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>68193204.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>68193204</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>136229985.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>46606279.72</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>46606279.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-1579885.667524114</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>68305837</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>68305837.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>67.64000000000001</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>57.23</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>57.23</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>59064123.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>84222262.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>84222262.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>140379245.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>45652449.62</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>45652449.62</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>1268393.578065202</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>59064123</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>59064123.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>67.8</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>61.76</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>56.91</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>56.91</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>55041164.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>115240085.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>115240085.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>153170422.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>44737206.8</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>44737206.8</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>6282247.801119044</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>55041164</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>55041164.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>68.92</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>61.16</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>56.6</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>77457284.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>149719715.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>149719715</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>157079528.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>44057108.44</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>44057108.44</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>13651562.01972742</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>77457284</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>77457284.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>69.28</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>60.56</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>56.31</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>60.56</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>56.31</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>81097612.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>180244870.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>180244870.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>161062192.7</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>42670813.98</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>42670813.98</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>21289870.83132054</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>81097612</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>81097612.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>69.06</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>59.93</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>55.99</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>59.93</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>55.99</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>148451128.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>204266767.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>204266767.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>153514394.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>41211816.88</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>41211816.88</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>31051352.88962071</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>148451128</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>148451128.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>68.47999999999999</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>59.37</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>55.7</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>59.37</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>55.7</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>214153238.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>196536229.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>196536229.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>140950400.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>38471387.22</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>38471387.22</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>36670902.22684878</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>214153238</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>214153238.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>67.32000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>58.69</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>55.39</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>55.39</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>227439313.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>191100759.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>191100759.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>120375958.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>34338500.78</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>34338500.78</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>36349642.98621568</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>227439313</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>227439313.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>64.8</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>57.81</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>54.98</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>54.98</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>230083062.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>164439341.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>164439341.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>98801936.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>30095348.66</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>30095348.66</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>33168991.64294642</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>230083062</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>230083062.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>62.72000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>57.11</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>54.65</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>54.65</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>201207096.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>141879514.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>141879514.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>76590805.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>26134633.24</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>26134633.24</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>27157338.34388511</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>201207096</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>201207096.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>60.27999999999999</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>56.46</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>54.4</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>109798437.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>102762022.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>102762022</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>57072853.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>22355997.5</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>22355997.5</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>20693210.76151591</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>109798437</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>109798437.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>701.8</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>734.15</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>644.12</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>734.15</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>644.12</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>2145406818.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>4705713538.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>4705713538.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>2697328683.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>2381458909.08</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>2381458909.08</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>47833880.16900253</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>2145406818</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>2145406818.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>712.8</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>729.6</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>642.32</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>729.6</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>642.3200000000001</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>2917531202.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>4446393537.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>4446393537.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>2537135784.1</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2394527724.36</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>2394527724.36</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>171300840.0050039</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>2917531202</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>2917531202.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>718.0</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>726.45</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>641.18</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>726.45</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>641.1799999999999</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>3308931687.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>3977678243.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>3977678243.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>2336901368.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>2356977274.04</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>2356977274.04</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>258836711.484827</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>3308931687</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>3308931687.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>724.4</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>720.75</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>639.48</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>720.75</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>639.48</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>9396894111.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>3406595539.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>3406595539.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>2092972596.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>2319670873.56</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>2319670873.56</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>332708021.9386873</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>9396894111</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>9396894111.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>731.2</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>715.55</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>638.3</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>715.55</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>638.3</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>5759803875.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1689450518.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1689450518.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1272693479.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>2149905312.46</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>2149905312.46</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-225925652.1964645</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>5759803875</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>5759803875.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>732.4</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>708.6</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>635.96</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>708.6</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>635.96</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>848806811.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>688943827.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>688943827.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>860708905.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>2069337538.82</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>2069337538.82</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-626216745.2396646</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>848806811</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>848806811.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>735.4</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>701.1</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>633.54</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>701.1</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>633.54</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>573954733.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>627878031.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>627878031</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1516353585.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>2106062606.14</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>2106062606.14</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-649518023.2571056</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>573954733</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>573954733.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>745.6</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>695.2</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>631.48</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>695.2</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>631.48</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>453518166.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>696124492.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>696124492.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>2883970531.7</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2126707687.18</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2126707687.18</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-630160054.0942674</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>453518166</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>453518166.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>752.0</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>688.05</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>628.72</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>688.05</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>628.72</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>811169006.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>779349653.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>779349653.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>4079717323.9</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2168937186.34</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2168937186.34</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-567096178.3225608</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>811169006</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>811169006.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>756.8</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>681.7</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>626.7</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>681.7</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>626.7</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>757270421.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>855936440.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>855936440.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>4864530439.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2227082877.5</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2227082877.5</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-495071225.1371737</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>757270421</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>757270421.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>760.8</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>624.74</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>673</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>624.74</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>543477829.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1032473983.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1032473983.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>5522062366.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>2292721646.52</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2292721646.52</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-368722471.2960072</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>543477829</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>543477829.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/電網營造.xlsx
+++ b/Result/checksun_type/電網營造.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】;【x】看好</t>
+          <t>【d1】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>571.972</t>
+          <t>495.404</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-19.05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,38 +1014,38 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>-0.58</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1054,26 +1054,26 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>101.5</v>
+        <v>101.42</v>
       </c>
       <c r="AN2" t="n">
-        <v>104.56</v>
+        <v>104.46</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>104.8</t>
+          <t>104.69</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.65</v>
+        <v>-0.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.09</t>
+          <t>-123.74</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>342622648.1473088</t>
+          <t>342245367.9695898</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>58435252.0</t>
+          <t>50590375.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>91261893.8</v>
+        <v>70167794.40000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>95235749.2</t>
+          <t>86685359.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>191448373.98</v>
+        <v>188576123.98</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3973855</t>
+          <t>-16517564</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-20206566.50086486</t>
+          <t>-21052695.26305016</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-25485065.37188588</t>
+          <t>-25706403.45506933</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>58435252.0</t>
+          <t>50590375.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>103.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>103.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,127 +1305,127 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>571.972</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>516.69</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-4.17</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-1.92</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>5.63</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>-0.98</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-10.10</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-0.96</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4.31</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.97</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.29</v>
+        <v>-0.58</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>102.7</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>101.54</v>
+        <v>101.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>104.68</v>
+        <v>104.56</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>104.89</t>
+          <t>104.8</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.21</v>
+        <v>-1.1</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-126.09</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>342622648.1473088</t>
+          <t>342245367.9695898</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>53428345.0</t>
+          <t>58435252.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>90868663.8</v>
+        <v>91261893.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>101082315.9</t>
+          <t>95235749.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>193362855.14</v>
+        <v>191448373.98</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-10213652</t>
+          <t>-3973855</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-19246839.43340649</t>
+          <t>-20206566.50086486</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-25099209.73977077</t>
+          <t>-25485065.37188588</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>53428345.0</t>
+          <t>58435252.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>646.583</t>
+          <t>516.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1757,12 +1757,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1873,18 +1873,18 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>96.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1894,30 +1894,30 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>101.62</v>
+        <v>101.54</v>
       </c>
       <c r="AN4" t="n">
-        <v>104.76</v>
+        <v>104.68</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>104.97</t>
+          <t>104.89</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.86</v>
+        <v>-0.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.34</v>
+        <v>-1.21</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-131.78</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>342622648.1473088</t>
+          <t>342245367.9695898</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>66712202.0</t>
+          <t>53428345.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>104630422.2</v>
+        <v>90868663.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>110389018.3</t>
+          <t>101082315.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>197447365.46</v>
+        <v>193362855.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5758596</t>
+          <t>-10213652</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-18182772.10497662</t>
+          <t>-19246839.43340649</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-23115132.73890021</t>
+          <t>-25099209.73977077</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>66712202.0</t>
+          <t>53428345.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1181.443</t>
+          <t>646.583</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2299,14 +2299,14 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.78</v>
+        <v>0.39</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2316,30 +2316,30 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>101.74</v>
+        <v>101.62</v>
       </c>
       <c r="AN5" t="n">
-        <v>104.83</v>
+        <v>104.76</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>105.04</t>
+          <t>104.97</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.04</v>
+        <v>-0.86</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.46</v>
+        <v>-1.34</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-134.64</t>
+          <t>-131.78</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>342622648.1473088</t>
+          <t>342245367.9695898</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>121672798.0</t>
+          <t>66712202.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>111924097.6</v>
+        <v>104630422.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>123203067.6</t>
+          <t>110389018.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>200134642.08</v>
+        <v>197447365.46</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-11278970</t>
+          <t>-5758596</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-17285979.26244506</t>
+          <t>-18182772.10497662</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-20878466.96126726</t>
+          <t>-23115132.73890021</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>121672798.0</t>
+          <t>66712202.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2559,7 +2559,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>6278</t>
@@ -2567,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1520.716</t>
+          <t>1181.443</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2582,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2592,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2667,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2677,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2698,17 +2702,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2717,47 +2721,47 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.49</v>
+        <v>0.78</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.29</v>
+        <v>0.45</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>101.8</v>
+        <v>101.74</v>
       </c>
       <c r="AN6" t="n">
-        <v>104.86</v>
+        <v>104.83</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>105.12</t>
+          <t>105.04</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.27</v>
+        <v>-1.04</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.56</v>
+        <v>-1.46</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2766,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-137.11</t>
+          <t>-134.64</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2776,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>342622648.1473088</t>
+          <t>342245367.9695898</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>156060872.0</t>
+          <t>121672798.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>103202924</v>
+        <v>111924097.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>132882164.3</t>
+          <t>123203067.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>201053456.9</v>
+        <v>200134642.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-29679240</t>
+          <t>-11278970</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-16632799.68084102</t>
+          <t>-17285979.26244506</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-22826205.88746065</t>
+          <t>-20878466.96126726</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>156060872.0</t>
+          <t>121672798.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2832,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2877,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2917,7 +2921,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2952,12 +2956,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2977,7 +2981,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>6278</t>
@@ -2985,42 +2993,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1520.716</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>550.832</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-38.29</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3085,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3095,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3116,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>91.87</t>
+          <t>96.38</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.81</v>
+        <v>0.49</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.43</v>
+        <v>-0.29</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>100.68</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>102.14</v>
+        <v>101.8</v>
       </c>
       <c r="AN7" t="n">
-        <v>104.91</v>
+        <v>104.86</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>105.22</t>
+          <t>105.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.43</v>
+        <v>-1.27</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.64</v>
+        <v>-1.56</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3184,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.87</t>
+          <t>-137.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3194,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>342622648.1473088</t>
+          <t>342245367.9695898</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>56469102.0</t>
+          <t>156060872.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>99209604.59999999</v>
+        <v>103202924</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>160755783.9</t>
+          <t>132882164.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>200342843.58</v>
+        <v>201053456.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-61546179</t>
+          <t>-29679240</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-15506725.825092</t>
+          <t>-16632799.68084102</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-28477904.92889903</t>
+          <t>-22826205.88746065</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>56469102.0</t>
+          <t>156060872.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3250,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3295,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3335,7 +3343,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3365,17 +3373,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>102.0</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>102.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3395,7 +3403,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>6278</t>
@@ -3403,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1199.573</t>
+          <t>550.832</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3433,12 +3445,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-36.74</t>
+          <t>-38.29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3513,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3534,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3549,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>66.62</t>
+          <t>91.87</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.62</v>
+        <v>1.81</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.58</v>
+        <v>-1.43</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>99.88</t>
+          <t>100.68</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>102.52</v>
+        <v>102.14</v>
       </c>
       <c r="AN8" t="n">
-        <v>104.95</v>
+        <v>104.91</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>105.27</t>
+          <t>105.22</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.67</v>
+        <v>-1.43</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.69</v>
+        <v>-1.64</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3602,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-140.09</t>
+          <t>-138.87</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3612,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>342622648.1473088</t>
+          <t>342245367.9695898</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>111295968</v>
+        <v>99209604.59999999</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>175945094.1</t>
+          <t>160755783.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>201620564.82</v>
+        <v>200342843.58</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-64649126</t>
+          <t>-61546179</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13148329.62439981</t>
+          <t>-15506725.825092</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-24864145.88349319</t>
+          <t>-28477904.92889903</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>122237137.0</t>
+          <t>56469102.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3713,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3753,7 +3765,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3778,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3815,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3825,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1025.601</t>
+          <t>1199.573</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3840,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3850,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-36.74</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3925,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3935,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>11.80</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3956,33 +3968,33 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>75.61</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.28</t>
+          <t>66.62</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.25</v>
+        <v>-2.58</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -3992,30 +4004,30 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.88</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>102.82</v>
+        <v>102.52</v>
       </c>
       <c r="AN9" t="n">
-        <v>105</v>
+        <v>104.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>105.32</t>
+          <t>105.27</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.96</v>
+        <v>-1.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.7</v>
+        <v>-1.69</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4024,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-140.20</t>
+          <t>-140.09</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4034,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>342622648.1473088</t>
+          <t>342245367.9695898</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>116147614.4</v>
+        <v>111295968</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>176548720.3</t>
+          <t>175945094.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>201428975.56</v>
+        <v>201620564.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-60401105</t>
+          <t>-64649126</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-11018181.21365556</t>
+          <t>-13148329.62439981</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-25860202.92993152</t>
+          <t>-24864145.88349319</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>103180579.0</t>
+          <t>122237137.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4090,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4135,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4175,7 +4187,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4200,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>101.0</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4247,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>785.188</t>
+          <t>1025.601</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4262,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4272,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-30.63</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4347,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4357,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4378,33 +4390,33 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>75.61</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.17</v>
+        <v>-3.25</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4414,30 +4426,30 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>98.94</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>103.24</v>
+        <v>102.82</v>
       </c>
       <c r="AN10" t="n">
-        <v>105.06</v>
+        <v>105</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>105.39</t>
+          <t>105.32</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-30.90</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-2.13</v>
+        <v>-1.96</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.63</v>
+        <v>-1.7</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4446,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.66</t>
+          <t>-140.20</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4456,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>342622648.1473088</t>
+          <t>342245367.9695898</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>134482037.6</v>
+        <v>116147614.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>193869170.8</t>
+          <t>176548720.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>205225010.12</v>
+        <v>201428975.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-59387133</t>
+          <t>-60401105</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8319631.810696295</t>
+          <t>-11018181.21365556</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-24317788.82020301</t>
+          <t>-25860202.92993152</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>78066930.0</t>
+          <t>103180579.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4512,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4557,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4567,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4597,7 +4609,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4622,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>98.7</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4669,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1386.529</t>
+          <t>785.188</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4684,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4694,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-30.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4769,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4779,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4800,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.83</v>
+        <v>0.57</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.8</v>
+        <v>-4.17</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>98.72</t>
+          <t>98.94</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>103.7</v>
+        <v>103.24</v>
       </c>
       <c r="AN11" t="n">
-        <v>105.23</v>
+        <v>105.06</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>105.47</t>
+          <t>105.39</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-44.85</t>
+          <t>-30.90</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-2.18</v>
+        <v>-2.13</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.5</v>
+        <v>-1.63</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4868,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-138.66</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4878,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>342622648.1473088</t>
+          <t>342245367.9695898</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>162561404.6</v>
+        <v>134482037.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>195664628.6</t>
+          <t>193869170.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>209197245.52</v>
+        <v>205225010.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-33103224</t>
+          <t>-59387133</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-5410875.990785983</t>
+          <t>-8319631.810696295</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-18555099.52701217</t>
+          <t>-24317788.82020301</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>136094275.0</t>
+          <t>78066930.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4934,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4979,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4989,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5019,7 +5031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5044,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5091,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1183.8</t>
+          <t>1386.529</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5106,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5116,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5191,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5201,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5222,17 +5234,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5241,47 +5253,47 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.4</v>
+        <v>-0.83</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5.18</v>
+        <v>-4.8</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.72</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>104.3</v>
+        <v>103.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>105.44</v>
+        <v>105.23</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>105.58</t>
+          <t>105.47</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-52.87</t>
+          <t>-44.85</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.04</v>
+        <v>-2.18</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.34</v>
+        <v>-1.5</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5290,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-131.67</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5300,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>342622648.1473088</t>
+          <t>342245367.9695898</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>222301963.2</v>
+        <v>162561404.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>191158060.8</t>
+          <t>195664628.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>220229469.28</v>
+        <v>209197245.52</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>31143902</t>
+          <t>-33103224</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3021017.166017586</t>
+          <t>-5410875.990785983</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-15877219.6607748</t>
+          <t>-18555099.52701217</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>116900919.0</t>
+          <t>136094275.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5356,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5411,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5441,7 +5453,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5466,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5513,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>716.145</t>
+          <t>342.197</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5528,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5543,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5613,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5623,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5644,66 +5656,66 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>36.88</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-2.38</v>
+        <v>-2.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>-1.38</v>
+        <v>-1.97</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>65.34</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>66.48</v>
+        <v>66.66</v>
       </c>
       <c r="AN13" t="n">
-        <v>59.51</v>
+        <v>59.74</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>57.59</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-30.43</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5712,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-43.62</t>
+          <t>-48.27</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5722,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>162980604.6905099</t>
+          <t>162796178.0219236</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45477092.0</t>
+          <t>21727300.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>71933724.59999999</v>
+        <v>69920675.40000001</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>62656210.3</t>
+          <t>59324823.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>54170058.14</v>
+        <v>54345060.02</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9277514</t>
+          <t>10595851</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-67230.60085528996</t>
+          <t>-1274911.192624518</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-4476473.566654816</t>
+          <t>-7917154.44735527</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>45477092.0</t>
+          <t>21727300.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5778,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5823,12 +5835,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5848,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5863,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5888,22 +5900,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5935,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1834.972</t>
+          <t>716.145</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5950,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5960,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6035,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6045,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6066,29 +6078,29 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>36.88</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>-3.79</v>
+        <v>-2.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.34</v>
+        <v>-1.38</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -6097,35 +6109,35 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.56</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>66.22</v>
+        <v>66.48</v>
       </c>
       <c r="AN14" t="n">
-        <v>59.29</v>
+        <v>59.51</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.41</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-23.79</t>
+          <t>-30.43</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6134,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-39.33</t>
+          <t>-43.62</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6144,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>162980604.6905099</t>
+          <t>162796178.0219236</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>119871452.0</t>
+          <t>45477092.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>69236552.40000001</v>
+        <v>71933724.59999999</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>65854229.5</t>
+          <t>62656210.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>53421696.84</v>
+        <v>54170058.14</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>3382322</t>
+          <t>9277514</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>734449.9383809876</t>
+          <t>-67230.60085528996</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1945961.681130782</t>
+          <t>-4476473.566654816</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>119871452.0</t>
+          <t>45477092.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6200,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6245,17 +6257,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6270,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6285,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6310,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6357,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1354.063</t>
+          <t>1834.972</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6372,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6382,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6457,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6467,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6488,17 +6500,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6507,47 +6519,47 @@
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>2.49</v>
+        <v>-3.79</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.08</v>
+        <v>-0.34</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>66.54</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>65.83</v>
+        <v>66.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>59.08</v>
+        <v>59.29</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>57.41</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-23.79</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6556,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-35.72</t>
+          <t>-39.33</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6566,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>162980604.6905099</t>
+          <t>162796178.0219236</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>91855404.0</t>
+          <t>119871452.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>55760487</v>
+        <v>69236552.40000001</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>61976845.5</t>
+          <t>65854229.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>51320392.56</v>
+        <v>53421696.84</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-6216358</t>
+          <t>3382322</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1221797.505564946</t>
+          <t>734449.9383809876</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-6232270.356056064</t>
+          <t>-1945961.681130782</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>91855404.0</t>
+          <t>119871452.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6622,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>12.99</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6667,17 +6679,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6692,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6707,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6732,22 +6744,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6779,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1059.506</t>
+          <t>1354.063</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6794,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6804,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-24.52</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6879,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6889,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6910,66 +6922,66 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>1.54</v>
+        <v>2.49</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>66.08</t>
+          <t>66.54</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>65.2</v>
+        <v>65.83</v>
       </c>
       <c r="AN16" t="n">
-        <v>58.76</v>
+        <v>59.08</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>57.22</t>
+          <t>57.34</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6978,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-33.57</t>
+          <t>-35.72</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -6988,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>162980604.6905099</t>
+          <t>162796178.0219236</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70672129.0</t>
+          <t>91855404.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>51050573.6</v>
+        <v>55760487</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>67636417.9</t>
+          <t>61976845.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>49798402.58</v>
+        <v>51320392.56</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-16585844</t>
+          <t>-6216358</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>2577082.57131422</t>
+          <t>1221797.505564946</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-9131267.9503759</t>
+          <t>-6232270.356056064</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>70672129.0</t>
+          <t>91855404.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7044,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>19.40</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7089,7 +7101,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7099,7 +7111,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7114,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7129,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7154,22 +7166,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7201,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>486.403</t>
+          <t>1059.506</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7216,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7226,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-40.56</t>
+          <t>-24.52</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7301,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7311,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7332,66 +7344,66 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>-1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>10.96</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.08</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>64.58</v>
+        <v>65.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>58.44</v>
+        <v>58.76</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>57.22</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-15.99</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AR17" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7400,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-30.95</t>
+          <t>-33.57</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7410,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>162980604.6905099</t>
+          <t>162796178.0219236</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>31792546.0</t>
+          <t>70672129.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>48728972.4</v>
+        <v>51050573.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>81984528.8</t>
+          <t>67636417.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>48567572.86</v>
+        <v>49798402.58</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-33255556</t>
+          <t>-16585844</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>4705873.575257879</t>
+          <t>2577082.57131422</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-10676939.76546222</t>
+          <t>-9131267.9503759</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>31792546.0</t>
+          <t>70672129.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7466,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>19.40</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7511,17 +7523,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7536,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7551,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7576,22 +7588,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7623,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>484.079</t>
+          <t>486.403</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7638,69 +7650,69 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-40.56</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>66.2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-3.44</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-47.44</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>0</t>
@@ -7723,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7733,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7754,17 +7766,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7773,47 +7785,47 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>-0.66</v>
+        <v>-1.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.96</v>
+        <v>2.45</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>66.64</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>64.09999999999999</v>
+        <v>64.58</v>
       </c>
       <c r="AN18" t="n">
-        <v>58.15</v>
+        <v>58.44</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-9.86</t>
+          <t>-15.99</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>2.82</v>
+        <v>2.52</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7822,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-28.19</t>
+          <t>-30.95</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7832,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>162980604.6905099</t>
+          <t>162796178.0219236</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>31991231.0</t>
+          <t>31792546.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>53378696</v>
+        <v>48728972.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>101549205.5</t>
+          <t>81984528.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>48028060.24</v>
+        <v>48567572.86</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-48170509</t>
+          <t>-33255556</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>7502748.728116079</t>
+          <t>4705873.575257879</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-8338053.473961905</t>
+          <t>-10676939.76546222</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>31991231.0</t>
+          <t>31792546.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7888,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7933,17 +7945,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -7958,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -7973,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -7998,22 +8010,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8045,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>800.087</t>
+          <t>484.079</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8070,22 +8082,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-48.52</t>
+          <t>-47.44</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -8125,7 +8137,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8140,7 +8152,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8155,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8176,203 +8188,203 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
+          <t>4.74</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>66.64</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-9.86</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-28.19</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>162796178.0219236</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>31991231.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>53378696</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>101549205.5</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>48028060.24</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-48170509</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>7502748.728116079</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-8338053.473961905</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>31991231.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>17.79</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>8.807108087502199</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>56.33331648044222</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>4.677783569058906</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
           <t>4.69</t>
         </is>
       </c>
-      <c r="AH19" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>9.82</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>66.9</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>63.52</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>57.84</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>56.89</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-5.47</t>
-        </is>
-      </c>
-      <c r="AQ19" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-26.41</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>162980604.6905099</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>52491125.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>62471906.6</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>121358388.6</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>47556857.96</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>-58886481</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>10382894.58303935</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>-4720287.39774853</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>52491125.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>17.79</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>洋華</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>8.807108087502199</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>56.33331648044222</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>4.677783569058906</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>4.69</t>
-        </is>
-      </c>
       <c r="BU19" t="inlineStr">
         <is>
           <t>3.20</t>
@@ -8380,7 +8392,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8395,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8420,17 +8432,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8457,7 +8469,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8467,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1021.167</t>
+          <t>800.087</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8482,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8492,17 +8504,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-49.94</t>
+          <t>-48.52</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8562,12 +8574,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8577,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>27.53</t>
+          <t>21.57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8598,66 +8610,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>-2.28</v>
+        <v>-1.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>7.14</v>
+        <v>5.32</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>67.44000000000001</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>62.95</v>
+        <v>63.52</v>
       </c>
       <c r="AN20" t="n">
-        <v>57.54</v>
+        <v>57.84</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>56.89</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8666,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-25.41</t>
+          <t>-26.41</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8676,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>162980604.6905099</t>
+          <t>162796178.0219236</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>68193204</v>
+        <v>62471906.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>136229985.7</t>
+          <t>121358388.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>46606279.72</v>
+        <v>47556857.96</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-68036781</t>
+          <t>-58886481</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>13128927.67045533</t>
+          <t>10382894.58303935</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1579885.667524114</t>
+          <t>-4720287.39774853</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>68305837.0</t>
+          <t>52491125.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8732,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.79</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8777,7 +8789,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8802,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8817,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8842,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8889,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>873.725</t>
+          <t>1021.167</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8904,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8914,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-40.00</t>
+          <t>-49.94</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -8984,12 +8996,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -8999,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>27.53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9020,63 +9032,63 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>-0.21</v>
+        <v>-2.28</v>
       </c>
       <c r="AI21" t="n">
-        <v>8.390000000000001</v>
+        <v>7.14</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>67.64000000000001</t>
+          <t>67.44000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>62.4</v>
+        <v>62.95</v>
       </c>
       <c r="AN21" t="n">
-        <v>57.23</v>
+        <v>57.54</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>56.65</t>
+          <t>56.77</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="AR21" t="n">
         <v>3.24</v>
@@ -9088,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-25.41</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9098,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>162980604.6905099</t>
+          <t>162796178.0219236</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>84222262.2</v>
+        <v>68193204</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>140379245.7</t>
+          <t>136229985.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>45652449.62</v>
+        <v>46606279.72</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-56156983</t>
+          <t>-68036781</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>15803257.36826977</t>
+          <t>13128927.67045533</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1268393.578065202</t>
+          <t>-1579885.667524114</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>59064123.0</t>
+          <t>68305837.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9154,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9199,7 +9211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9209,7 +9221,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9224,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9239,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9264,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9311,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>809.417</t>
+          <t>873.725</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9326,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9336,17 +9348,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-24.76</t>
+          <t>-40.00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9406,12 +9418,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>14.43</t>
+          <t>14.60</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9421,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9442,66 +9454,66 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>50.95</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>-0.59</v>
+        <v>-0.21</v>
       </c>
       <c r="AI22" t="n">
-        <v>9.779999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
+          <t>9.05</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>67.64000000000001</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>56.65</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
           <t>8.51</t>
         </is>
       </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="AM22" t="n">
-        <v>61.76</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>56.52</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
-      </c>
       <c r="AQ22" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.17</v>
+        <v>3.24</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9510,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-27.02</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9520,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>162980604.6905099</t>
+          <t>162796178.0219236</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>115240085.2</v>
+        <v>84222262.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>153170422.4</t>
+          <t>140379245.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>44737206.8</v>
+        <v>45652449.62</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-37930337</t>
+          <t>-56156983</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>18445959.87557969</t>
+          <t>15803257.36826977</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>6282247.801119044</t>
+          <t>1268393.578065202</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>55041164.0</t>
+          <t>59064123.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9576,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9621,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9646,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9661,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9686,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9733,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1151.287</t>
+          <t>809.417</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9748,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9758,17 +9770,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-24.76</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9828,12 +9840,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>14.43</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9843,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9864,66 +9876,66 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>57.27</t>
+          <t>50.95</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>-2.06</v>
+        <v>-0.59</v>
       </c>
       <c r="AI23" t="n">
-        <v>12.69</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>61.16</v>
+        <v>61.76</v>
       </c>
       <c r="AN23" t="n">
-        <v>56.6</v>
+        <v>56.91</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>56.36</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9932,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-29.75</t>
+          <t>-27.02</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9942,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>162980604.6905099</t>
+          <t>162796178.0219236</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>149719715</v>
+        <v>115240085.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>157079528.3</t>
+          <t>153170422.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>44057108.44</v>
+        <v>44737206.8</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-7359813</t>
+          <t>-37930337</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>20657543.88911799</t>
+          <t>18445959.87557969</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>13651562.01972742</t>
+          <t>6282247.801119044</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>77457284.0</t>
+          <t>55041164.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -9998,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10043,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10068,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10083,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>80.27</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10108,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10155,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1736.086</t>
+          <t>3187.546</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10170,7 +10182,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>716.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10185,12 +10197,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-24.85</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10255,7 +10267,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10265,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10286,66 +10298,66 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>66.19</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="AI24" t="n">
-        <v>-2.08</v>
+        <v>-1.48</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>706.2</t>
+          <t>707.8</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>721.2</v>
+        <v>718.45</v>
       </c>
       <c r="AN24" t="n">
-        <v>660.24</v>
+        <v>662.8200000000001</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>642.91</t>
+          <t>643.56</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-39.98</t>
+          <t>-35.95</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>7.82</v>
+        <v>7.65</v>
       </c>
       <c r="AR24" t="n">
-        <v>13.02</v>
+        <v>11.95</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10354,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-83.87</t>
+          <t>-85.20</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10364,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>1840994094</v>
+        <v>1791250542.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>2486803181.6</t>
+          <t>2383687512.6</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>2593471789.5</v>
+        <v>2625926244.44</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-645809087</t>
+          <t>-592436970</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-87575595.74692756</t>
+          <t>-113490037.7497351</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-295436683.9736991</t>
+          <t>-256019468.7651763</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>1240653794.0</t>
+          <t>2277774997.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10420,7 +10432,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-7.38</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10465,17 +10477,17 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
@@ -10490,7 +10502,7 @@
       </c>
       <c r="BV24" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW24" t="inlineStr">
@@ -10505,12 +10517,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10530,22 +10542,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="CE24" t="inlineStr">
+        <is>
+          <t>730.0</t>
+        </is>
+      </c>
+      <c r="CF24" t="inlineStr">
+        <is>
+          <t>704.0</t>
+        </is>
+      </c>
+      <c r="CG24" t="inlineStr">
+        <is>
           <t>715.0</t>
-        </is>
-      </c>
-      <c r="CE24" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="CF24" t="inlineStr">
-        <is>
-          <t>708.0</t>
-        </is>
-      </c>
-      <c r="CG24" t="inlineStr">
-        <is>
-          <t>716.0</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10577,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2409.738</t>
+          <t>1736.086</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10592,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10602,17 +10614,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-32.61</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10677,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10687,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10708,66 +10720,66 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
+          <t>72.92</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>43.94</t>
-        </is>
-      </c>
       <c r="AH25" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AI25" t="n">
-        <v>-2.73</v>
+        <v>-2.08</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>706.2</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>722.7</v>
+        <v>721.2</v>
       </c>
       <c r="AN25" t="n">
-        <v>657.66</v>
+        <v>660.24</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>642.4</t>
+          <t>642.91</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>-45.49</t>
+          <t>-39.98</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>7.81</v>
+        <v>7.82</v>
       </c>
       <c r="AR25" t="n">
-        <v>14.33</v>
+        <v>13.02</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10776,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-82.26</t>
+          <t>-83.87</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10786,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>2225561827.2</v>
+        <v>1840994094</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>3302427213.3</t>
+          <t>2486803181.6</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>2578743388.1</v>
+        <v>2593471789.5</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-1076865386</t>
+          <t>-645809087</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-49782670.61478729</t>
+          <t>-87575595.74692756</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-230075552.3796711</t>
+          <t>-295436683.9736991</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>1706016743.0</t>
+          <t>1240653794.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10842,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10887,17 +10899,17 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -10912,7 +10924,7 @@
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
@@ -10927,12 +10939,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -10952,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>715.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>694.0</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>716.0</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -10999,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1813.678</t>
+          <t>2409.738</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11014,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11024,17 +11036,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-32.61</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11099,7 +11111,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11109,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11130,66 +11142,66 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>52.08</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>43.94</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>-0.08</v>
+        <v>1.14</v>
       </c>
       <c r="AI26" t="n">
-        <v>-2.59</v>
+        <v>-2.73</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>706.6</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>725.4</v>
+        <v>722.7</v>
       </c>
       <c r="AN26" t="n">
-        <v>655.24</v>
+        <v>657.66</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>641.96</t>
+          <t>642.4</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>-48.64</t>
+          <t>-45.49</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>8.19</v>
+        <v>7.81</v>
       </c>
       <c r="AR26" t="n">
-        <v>15.96</v>
+        <v>14.33</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11198,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-82.26</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11208,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>2709898314.4</v>
+        <v>2225561827.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>3707805926.5</t>
+          <t>3302427213.3</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>2561747225.36</v>
+        <v>2578743388.1</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-997907612</t>
+          <t>-1076865386</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-17002146.65753568</t>
+          <t>-49782670.61478729</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-178345839.1960711</t>
+          <t>-230075552.3796711</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>1267840540.0</t>
+          <t>1706016743.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11264,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11309,17 +11321,17 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11334,7 +11346,7 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
@@ -11349,12 +11361,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11374,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>703.0</t>
+          <t>705.0</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>715.0</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>694.0</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11421,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3516.568</t>
+          <t>1813.678</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11436,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11446,17 +11458,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-21.29</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11521,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11531,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11552,66 +11564,66 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>52.08</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>-1.9</v>
+        <v>-0.08</v>
       </c>
       <c r="AI27" t="n">
-        <v>-3.42</v>
+        <v>-2.59</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>704.4</t>
+          <t>706.6</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>729.35</v>
+        <v>725.4</v>
       </c>
       <c r="AN27" t="n">
-        <v>653</v>
+        <v>655.24</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>641.5</t>
+          <t>641.96</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>-49.29</t>
+          <t>-48.64</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>9.08</v>
+        <v>8.19</v>
       </c>
       <c r="AR27" t="n">
-        <v>17.9</v>
+        <v>15.96</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11620,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-77.84</t>
+          <t>-80.24</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11630,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>2885411570</v>
+        <v>2709898314.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>3665902553.6</t>
+          <t>3707805926.5</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>2552773254.62</v>
+        <v>2561747225.36</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-780490983</t>
+          <t>-997907612</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>12333070.16765259</t>
+          <t>-17002146.65753568</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-51129304.35535431</t>
+          <t>-178345839.1960711</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>2463966639.0</t>
+          <t>1267840540.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11686,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-10.49</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11731,17 +11743,17 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11756,7 +11768,7 @@
       </c>
       <c r="BV27" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW27" t="inlineStr">
@@ -11771,12 +11783,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -11796,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>711.0</t>
+          <t>703.0</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11843,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3523.66</t>
+          <t>3516.568</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11858,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11868,17 +11880,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-21.29</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11943,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11953,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11974,66 +11986,66 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>27.49</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>0.65</v>
+        <v>-1.9</v>
       </c>
       <c r="AI28" t="n">
-        <v>-4.23</v>
+        <v>-3.42</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>702.4</t>
+          <t>704.4</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>733.4</v>
+        <v>729.35</v>
       </c>
       <c r="AN28" t="n">
-        <v>650.8200000000001</v>
+        <v>653</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>641.01</t>
+          <t>641.5</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>-42.31</t>
+          <t>-49.29</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>11.6</v>
+        <v>9.08</v>
       </c>
       <c r="AR28" t="n">
-        <v>20.1</v>
+        <v>17.9</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12042,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-75.11</t>
+          <t>-77.84</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12052,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>2976124482.6</v>
+        <v>2885411570</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>3476901363.0</t>
+          <t>3665902553.6</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>2522196255.28</v>
+        <v>2552773254.62</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-500776880</t>
+          <t>-780490983</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>23871683.71729021</t>
+          <t>12333070.16765259</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>4278281.394074917</t>
+          <t>-51129304.35535431</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>2526492754.0</t>
+          <t>2463966639.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12108,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-10.49</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12153,17 +12165,17 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12178,7 +12190,7 @@
       </c>
       <c r="BV28" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW28" t="inlineStr">
@@ -12193,12 +12205,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12218,22 +12230,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>717.0</t>
+          <t>711.0</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>727.0</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>707.0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12265,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4456.494</t>
+          <t>3523.66</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12280,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12290,17 +12302,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12365,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12375,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12396,66 +12408,66 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>-0.31</v>
+        <v>0.65</v>
       </c>
       <c r="AI29" t="n">
-        <v>-4.77</v>
+        <v>-4.23</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>702.2</t>
+          <t>702.4</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>737.35</v>
+        <v>733.4</v>
       </c>
       <c r="AN29" t="n">
-        <v>648.52</v>
+        <v>650.8200000000001</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>640.28</t>
+          <t>641.01</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-41.44</t>
+          <t>-42.31</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>13.01</v>
+        <v>11.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>22.23</v>
+        <v>20.1</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
@@ -12464,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-72.48</t>
+          <t>-75.11</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12474,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>3132612269.2</v>
+        <v>2976124482.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>3269603904.2</t>
+          <t>3476901363.0</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>2494838192.4</v>
+        <v>2522196255.28</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-136991635</t>
+          <t>-500776880</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>27434120.50332935</t>
+          <t>23871683.71729021</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>76579952.95061398</t>
+          <t>4278281.394074917</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>3163492460.0</t>
+          <t>2526492754.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12530,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12575,7 +12587,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12585,7 +12597,7 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12600,7 +12612,7 @@
       </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW29" t="inlineStr">
@@ -12615,12 +12627,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12640,22 +12652,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>717.0</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>738.0</t>
+          <t>727.0</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>707.0</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12687,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5678.126</t>
+          <t>4456.494</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12702,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12712,17 +12724,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12787,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12797,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>15.89</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12818,66 +12830,66 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>4.17</v>
+        <v>-0.31</v>
       </c>
       <c r="AI30" t="n">
-        <v>-5.19</v>
+        <v>-4.77</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>699.8</t>
+          <t>702.2</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>738.1</v>
+        <v>737.35</v>
       </c>
       <c r="AN30" t="n">
-        <v>646.54</v>
+        <v>648.52</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>639.58</t>
+          <t>640.28</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-41.44</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>15.35</v>
+        <v>13.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>24.53</v>
+        <v>22.23</v>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
@@ -12886,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-69.62</t>
+          <t>-72.48</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12896,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>4379292599.4</v>
+        <v>3132612269.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>3034371558.8</t>
+          <t>3269603904.2</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>2446536212.66</v>
+        <v>2494838192.4</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>1344921040</t>
+          <t>-136991635</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>18498514.60382305</t>
+          <t>27434120.50332935</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>108883088.3545771</t>
+          <t>76579952.95061398</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>4127699179.0</t>
+          <t>3163492460.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12952,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -12997,17 +13009,17 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>26.28</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13022,7 +13034,7 @@
       </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW30" t="inlineStr">
@@ -13037,12 +13049,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13062,22 +13074,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>704.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13109,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3102.28</t>
+          <t>5678.126</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13124,7 +13136,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13134,17 +13146,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13209,7 +13221,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13219,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13240,66 +13252,66 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>-0.97</v>
+        <v>4.17</v>
       </c>
       <c r="AI31" t="n">
-        <v>-4.41</v>
+        <v>-5.19</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>701.8</t>
+          <t>699.8</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>734.15</v>
+        <v>738.1</v>
       </c>
       <c r="AN31" t="n">
-        <v>644.12</v>
+        <v>646.54</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>638.67</t>
+          <t>639.58</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-37.42</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>15.15</v>
+        <v>15.35</v>
       </c>
       <c r="AR31" t="n">
-        <v>26.82</v>
+        <v>24.53</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13308,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-66.78</t>
+          <t>-69.62</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13318,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>4705713538.6</v>
+        <v>4379292599.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>2697328683.0</t>
+          <t>3034371558.8</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>2381458909.08</v>
+        <v>2446536212.66</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>2008384855</t>
+          <t>1344921040</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>2064955.740049592</t>
+          <t>18498514.60382305</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>47833880.16900253</t>
+          <t>108883088.3545771</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>2145406818.0</t>
+          <t>4127699179.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13374,7 +13386,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13419,17 +13431,17 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>26.28</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13444,7 +13456,7 @@
       </c>
       <c r="BV31" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW31" t="inlineStr">
@@ -13459,12 +13471,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13484,22 +13496,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
+          <t>743.0</t>
+        </is>
+      </c>
+      <c r="CF31" t="inlineStr">
+        <is>
           <t>704.0</t>
         </is>
       </c>
-      <c r="CF31" t="inlineStr">
-        <is>
-          <t>677.0</t>
-        </is>
-      </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>695.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13531,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4210.877</t>
+          <t>3102.28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13546,7 +13558,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13556,17 +13568,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13631,7 +13643,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-7.72</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13641,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13662,66 +13674,66 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>-4.46</v>
+        <v>-0.97</v>
       </c>
       <c r="AI32" t="n">
-        <v>-2.3</v>
+        <v>-4.41</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>712.8</t>
+          <t>701.8</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>729.6</v>
+        <v>734.15</v>
       </c>
       <c r="AN32" t="n">
-        <v>642.3200000000001</v>
+        <v>644.12</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>638.33</t>
+          <t>638.67</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-38.99</t>
+          <t>-43.51</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>18.15</v>
+        <v>15.15</v>
       </c>
       <c r="AR32" t="n">
-        <v>29.74</v>
+        <v>26.82</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -13730,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-63.17</t>
+          <t>-66.78</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13740,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>4446393537.2</v>
+        <v>4705713538.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>2537135784.1</t>
+          <t>2697328683.0</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>2394527724.36</v>
+        <v>2381458909.08</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>1909257753</t>
+          <t>2008384855</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-6256666.883396398</t>
+          <t>2064955.740049592</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>171300840.0050039</t>
+          <t>47833880.16900253</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>2917531202.0</t>
+          <t>2145406818.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13796,7 +13808,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-11.79</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -13846,12 +13858,12 @@
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -13866,7 +13878,7 @@
       </c>
       <c r="BV32" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW32" t="inlineStr">
@@ -13881,12 +13893,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -13906,12 +13918,12 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>704.0</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
@@ -13921,7 +13933,7 @@
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>695.0</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -13953,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4656.178</t>
+          <t>4210.877</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13968,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13978,17 +13990,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>70.21</t>
+          <t>75.25</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14053,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-7.72</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14063,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14084,66 +14096,66 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>-1.67</v>
+        <v>-4.46</v>
       </c>
       <c r="AI33" t="n">
-        <v>-1.16</v>
+        <v>-2.3</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.59</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>718.0</t>
+          <t>712.8</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>726.45</v>
+        <v>729.6</v>
       </c>
       <c r="AN33" t="n">
-        <v>641.1799999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>638.1</t>
+          <t>638.33</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-29.15</t>
+          <t>-38.99</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>23.12</v>
+        <v>18.15</v>
       </c>
       <c r="AR33" t="n">
-        <v>32.64</v>
+        <v>29.74</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -14152,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-59.58</t>
+          <t>-63.17</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14162,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>3977678243.4</v>
+        <v>4446393537.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>2336901368.1</t>
+          <t>2537135784.1</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>2356977274.04</v>
+        <v>2394527724.36</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>1640776875</t>
+          <t>1909257753</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-38539849.95401464</t>
+          <t>-6256666.883396398</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>258836711.484827</t>
+          <t>171300840.0050039</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>3308931687.0</t>
+          <t>2917531202.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14218,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.79</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14273,7 +14285,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14288,7 +14300,7 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
@@ -14303,12 +14315,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14328,22 +14340,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>701.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>729.0</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>677.0</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>706.0</t>
+          <t>681.0</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14375,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12908.308</t>
+          <t>4656.178</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14390,7 +14402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14400,17 +14412,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70.21</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14475,7 +14487,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-4.34</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14485,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14506,66 +14518,66 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>-5.02</v>
+        <v>-1.67</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.51</v>
+        <v>-1.16</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>724.4</t>
+          <t>718.0</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>720.75</v>
+        <v>726.45</v>
       </c>
       <c r="AN34" t="n">
-        <v>639.48</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>637.48</t>
+          <t>638.1</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-24.05</t>
+          <t>-29.15</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>26.6</v>
+        <v>23.12</v>
       </c>
       <c r="AR34" t="n">
-        <v>35.02</v>
+        <v>32.64</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14574,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-56.63</t>
+          <t>-59.58</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14584,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>4919856794.394476</t>
+          <t>4917730635.55587</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>3406595539.2</v>
+        <v>3977678243.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>2092972596.2</t>
+          <t>2336901368.1</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>2319670873.56</v>
+        <v>2356977274.04</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>1313622943</t>
+          <t>1640776875</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-92608315.67016768</t>
+          <t>-38539849.95401464</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>332708021.9386873</t>
+          <t>258836711.484827</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>9396894111.0</t>
+          <t>3308931687.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14640,7 +14652,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14685,7 +14697,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14695,7 +14707,7 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>24.80</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -14710,7 +14722,7 @@
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>52.53</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
@@ -14725,12 +14737,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>226170</t>
+          <t>225854</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -14750,22 +14762,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>721.0</t>
+          <t>701.0</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>729.0</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>698.0</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>706.0</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/電網營造.xlsx
+++ b/Result/checksun_type/電網營造.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW31"/>
+  <dimension ref="A1:CW28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】;【x】看好</t>
+          <t>【d2】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6854.831</t>
+          <t>2329.335</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1118,22 +1118,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2025-11-06 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>67.43</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>65.38</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.95</v>
+        <v>-0.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>-3.76</v>
+        <v>-2.69</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>94.46000000000001</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>98.15000000000001</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>101.78</v>
+        <v>101.26</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.02</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-2.04</v>
+        <v>-1.91</v>
       </c>
       <c r="BE2" t="n">
-        <v>-1.9</v>
+        <v>-1.91</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,53 +1212,53 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-145.03</t>
+          <t>-145.26</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>340409143.932133</t>
+          <t>392739532.1134021</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>667543889.0</t>
+          <t>221175245.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>251898102.2</v>
+        <v>287216689.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>210921622.4</t>
+          <t>222565975.8</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>193065355.42</v>
+        <v>189489206.36</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>40976479</t>
+          <t>64650713</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>7144030.417056534</t>
+          <t>14842795.73044402</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>43132699.40067032</t>
+          <t>31144899.34932396</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>667543889.0</t>
+          <t>221175245.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>95.9</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1261.569</t>
+          <t>2622.443</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>17.81</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.23</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2025-11-06 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>25.80</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>61.67</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.13</v>
+        <v>0.82</v>
       </c>
       <c r="AV3" t="n">
-        <v>-3.98</v>
+        <v>-3.22</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>94.52</t>
+          <t>94.62</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>98.44</v>
+        <v>97.77</v>
       </c>
       <c r="BA3" t="n">
-        <v>101.97</v>
+        <v>101.55</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.17</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-19.62</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-2.23</v>
+        <v>-1.95</v>
       </c>
       <c r="BE3" t="n">
-        <v>-1.86</v>
+        <v>-1.91</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,53 +1699,53 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-144.17</t>
+          <t>-145.27</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>340409143.932133</t>
+          <t>392739532.1134021</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>118545782.0</t>
+          <t>250215435.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>139481674</v>
+        <v>261125039.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>154174301.4</t>
+          <t>221655466.3</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>181554361.68</v>
+        <v>194260067.76</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-14692627</t>
+          <t>39469573</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>600636.0563994827</t>
+          <t>11878776.89064767</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>4325364.215319782</t>
+          <t>37919882.49539891</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>118545782.0</t>
+          <t>250215435.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1915.001</t>
+          <t>6854.831</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.67</t>
+          <t>-7.40</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2025-11-06 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>67.43</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.83</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AV4" t="n">
-        <v>-4.11</v>
+        <v>-3.76</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>94.78</t>
+          <t>94.46</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>98.84</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="BA4" t="n">
-        <v>102.2</v>
+        <v>101.78</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>103.54</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-26.27</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-2.24</v>
+        <v>-2.04</v>
       </c>
       <c r="BE4" t="n">
-        <v>-1.77</v>
+        <v>-1.9</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,53 +2186,53 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-142.00</t>
+          <t>-145.03</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>340409143.932133</t>
+          <t>392739532.1134021</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>178603097.0</t>
+          <t>667543889.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>170861417</v>
+        <v>251898102.2</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>149993947.3</t>
+          <t>210921622.4</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>181112287.28</v>
+        <v>193065355.42</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>20867469</t>
+          <t>40976479</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-76587.24522239016</t>
+          <t>7144030.417056534</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>7553062.407129079</t>
+          <t>43132699.40067032</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>178603097.0</t>
+          <t>667543889.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>959.354</t>
+          <t>1261.569</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-9.23</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2579,22 +2579,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2025-11-06 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.55</v>
+        <v>-0.13</v>
       </c>
       <c r="AV5" t="n">
-        <v>-3.77</v>
+        <v>-3.98</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>95.58</t>
+          <t>94.52000000000001</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>99.31999999999999</v>
+        <v>98.44</v>
       </c>
       <c r="BA5" t="n">
-        <v>102.46</v>
+        <v>101.97</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>103.72</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-24.62</t>
+          <t>-19.62</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-2.06</v>
+        <v>-2.23</v>
       </c>
       <c r="BE5" t="n">
-        <v>-1.66</v>
+        <v>-1.86</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,53 +2673,53 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-139.25</t>
+          <t>-144.17</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>340409143.932133</t>
+          <t>392739532.1134021</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>90716995.0</t>
+          <t>118545782.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>157915262</v>
+        <v>139481674</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>141020232.6</t>
+          <t>154174301.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>180088637.34</v>
+        <v>181554361.68</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>16895029</t>
+          <t>-14692627</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1463796.272922657</t>
+          <t>600636.0563994827</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>5459595.273744881</t>
+          <t>4325364.215319782</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>90716995.0</t>
+          <t>118545782.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2143.275</t>
+          <t>1915.001</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2025-11-06 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,51 +3107,51 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.46</v>
+        <v>-1.98</v>
       </c>
       <c r="AV6" t="n">
-        <v>-3.68</v>
+        <v>-4.11</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>94.78</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>99.66</v>
+        <v>98.84</v>
       </c>
       <c r="BA6" t="n">
-        <v>102.66</v>
+        <v>102.2</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>103.54</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-24.42</t>
+          <t>-26.27</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-1.93</v>
+        <v>-2.24</v>
       </c>
       <c r="BE6" t="n">
-        <v>-1.55</v>
+        <v>-1.77</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,53 +3160,53 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-136.83</t>
+          <t>-142.01</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>340409143.932133</t>
+          <t>392739532.1134021</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>204080748.0</t>
+          <t>178603097.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>182185893</v>
+        <v>170861417</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>141914016.9</t>
+          <t>149993947.3</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>182085275.32</v>
+        <v>181112287.28</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>40271876</t>
+          <t>20867469</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-2722594.735953119</t>
+          <t>-76587.24522239016</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>11690310.46627656</t>
+          <t>7553062.407129079</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>204080748.0</t>
+          <t>178603097.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1095.019</t>
+          <t>959.354</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3553,22 +3553,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2025-11-06 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.29</v>
+        <v>-1.55</v>
       </c>
       <c r="AV7" t="n">
-        <v>-3.59</v>
+        <v>-3.77</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>96.32</t>
+          <t>95.58</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>99.91</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="BA7" t="n">
-        <v>102.92</v>
+        <v>102.46</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>104.03</t>
+          <t>103.72</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-22.67</t>
+          <t>-24.62</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-1.79</v>
+        <v>-2.06</v>
       </c>
       <c r="BE7" t="n">
-        <v>-1.46</v>
+        <v>-1.66</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,53 +3647,53 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-134.58</t>
+          <t>-139.25</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>340409143.932133</t>
+          <t>392739532.1134021</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>105461748.0</t>
+          <t>90716995.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>169945142.6</v>
+        <v>157915262</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>127912733.2</t>
+          <t>141020232.6</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>181934477.5</v>
+        <v>180088637.34</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>42032409</t>
+          <t>16895029</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-5343122.954540333</t>
+          <t>-1463796.272922657</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>8027704.6889548</t>
+          <t>5459595.273744881</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>105461748.0</t>
+          <t>90716995.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2867.432</t>
+          <t>2143.275</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.98</t>
+          <t>-9.04</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2025-11-06 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>21.08</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4081,51 +4081,51 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.89</v>
+        <v>-1.46</v>
       </c>
       <c r="AV8" t="n">
-        <v>-3.42</v>
+        <v>-3.68</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>96.56</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>99.98</v>
+        <v>99.66</v>
       </c>
       <c r="BA8" t="n">
-        <v>103.16</v>
+        <v>102.66</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>104.11</t>
+          <t>103.89</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-29.65</t>
+          <t>-24.42</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-1.78</v>
+        <v>-1.93</v>
       </c>
       <c r="BE8" t="n">
-        <v>-1.38</v>
+        <v>-1.55</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,53 +4134,53 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-132.62</t>
+          <t>-136.83</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>340409143.932133</t>
+          <t>392739532.1134021</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>275444497.0</t>
+          <t>204080748.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>168866928.8</v>
+        <v>182185893</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>122425595.9</t>
+          <t>141914016.9</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>187955938.86</v>
+        <v>182085275.32</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>46441332</t>
+          <t>40271876</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-7774182.526084903</t>
+          <t>-2722594.735953119</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>13075028.4110325</t>
+          <t>11690310.46627656</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>275444497.0</t>
+          <t>204080748.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-10.75</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1176.217</t>
+          <t>1095.019</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>28.20</t>
+          <t>32.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4527,22 +4527,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2025-11-06 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>10.77</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.29</v>
+        <v>0.29</v>
       </c>
       <c r="AV9" t="n">
-        <v>-2.93</v>
+        <v>-3.59</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>97.17999999999999</t>
+          <t>96.32000000000001</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>100.12</v>
+        <v>99.91</v>
       </c>
       <c r="BA9" t="n">
-        <v>103.4</v>
+        <v>102.92</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>104.21</t>
+          <t>104.03</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-30.26</t>
+          <t>-22.67</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-1.66</v>
+        <v>-1.79</v>
       </c>
       <c r="BE9" t="n">
-        <v>-1.27</v>
+        <v>-1.46</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,53 +4621,53 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-130.20</t>
+          <t>-134.58</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>340409143.932133</t>
+          <t>392739532.1134021</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>113872322.0</t>
+          <t>105461748.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>129126477.6</v>
+        <v>169945142.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>100724671.4</t>
+          <t>127912733.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>186955581.28</v>
+        <v>181934477.5</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>28401806</t>
+          <t>42032409</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-11564948.15101534</t>
+          <t>-5343122.954540333</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>1606088.177892312</t>
+          <t>8027704.6889548</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>113872322.0</t>
+          <t>105461748.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2192.219</t>
+          <t>2867.432</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>31.10</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-7.98</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2025-11-06 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5055,51 +5055,51 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-1.54</v>
+        <v>-0.89</v>
       </c>
       <c r="AV10" t="n">
-        <v>-2.59</v>
+        <v>-3.42</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>96.56</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>100.3</v>
+        <v>99.98</v>
       </c>
       <c r="BA10" t="n">
-        <v>103.57</v>
+        <v>103.16</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>104.27</t>
+          <t>104.11</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-35.75</t>
+          <t>-29.65</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-1.6</v>
+        <v>-1.78</v>
       </c>
       <c r="BE10" t="n">
-        <v>-1.18</v>
+        <v>-1.38</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,53 +5108,53 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-127.92</t>
+          <t>-132.62</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2026/01/02</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>340409143.932133</t>
+          <t>392739532.1134021</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>212070150.0</t>
+          <t>275444497.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>124125203.2</v>
+        <v>168866928.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>94680273.7</t>
+          <t>122425595.9</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>186134840.46</v>
+        <v>187955938.86</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>29444929</t>
+          <t>46441332</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-13959682.02899855</t>
+          <t>-7774182.526084903</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>2475832.017053053</t>
+          <t>13075028.4110325</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>212070150.0</t>
+          <t>275444497.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-9.72</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
+          <t>96.8</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
           <t>97.4</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>98.1</t>
-        </is>
-      </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5321,22 +5321,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1475.997</t>
+          <t>243.137</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,37 +5376,37 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2025-10-21 00:00:00</t>
+          <t>2025-11-07 00:00:00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-08-04 00:00:00</t>
+          <t>2025-10-27 00:00:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-08-14 00:00:00</t>
+          <t>2025-10-29 00:00:00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5431,22 +5431,22 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025/09/19</t>
+          <t>2025/07/15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -5456,67 +5456,67 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2025/11/18</t>
+          <t>2025/09/09</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025/10/02</t>
+          <t>2025/07/08</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025/12/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/10/29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-11-04 00:00:00</t>
+          <t>2024-09-24 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,121 +5527,121 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-2.2</v>
+        <v>0.06</v>
       </c>
       <c r="AV11" t="n">
-        <v>-2.03</v>
+        <v>-1.89</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>98.36</t>
+          <t>62.76000000000001</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>100.4</v>
+        <v>63.97</v>
       </c>
       <c r="BA11" t="n">
-        <v>103.72</v>
+        <v>62.96</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>104.34</t>
+          <t>59.36</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-33.01</t>
+          <t>-208.68</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-1.43</v>
+        <v>-0.23</v>
       </c>
       <c r="BE11" t="n">
-        <v>-1.07</v>
+        <v>0.21</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-125.42</t>
+          <t>-94.87</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/11/07</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>340409143.932133</t>
+          <t>206888555.6845361</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>142876996.0</t>
+          <t>15240166.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>101642140.8</v>
+        <v>20787836</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>80144478.9</t>
+          <t>24794617.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>182945328.64</v>
+        <v>60037749.24</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>21497661</t>
+          <t>-4006781</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-16947957.31009884</t>
+          <t>-6593936.653894514</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-6891295.213326335</t>
+          <t>-6288013.214195162</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>142876996.0</t>
+          <t>15240166.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5651,27 +5651,27 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2025/10/16</t>
+          <t>2025/10/22</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>洋華</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>洋華</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
@@ -5686,27 +5686,27 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>-11.06846749116489</t>
+          <t>8.807108087502199</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>5.933446073116056</t>
+          <t>56.33331648044222</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>12.2962952682113</t>
+          <t>4.677783569058906</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,87 +5716,87 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>12.67%</t>
+          <t>45.67%</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>7.38%</t>
+          <t>32.78%</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>其他40.98%、光電產品39.78%、LED燈條(板)19.25% (2024年)</t>
+          <t>電線電纜器材81.50%、觸控面板18.50% (2024年)</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>台表科-光電業-上市</t>
+          <t>洋華-光電業-上市</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>光電業右下上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="CV11" t="inlineStr">
         <is>
-          <t>** 平面顯示器 - 背光模組、面板、顯示器模組** LED照明產業 - 藍寶石晶圓/晶片、生產製程、檢測設備及原物料、光源/磊晶、封裝/模組、燈具/應用** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件、電動汽車、電動機車、電動自行車** 能源元件 - 原材料、電池芯、電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造、電網維運、高壓AMI、低壓AMI、能源管理服務、系統整合服務、電力零售業</t>
+          <t>** 觸控面板 - 觸控面板** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造、電網維運、高壓AMI、低壓AMI、能源管理服務、系統整合服務、電力零售業</t>
         </is>
       </c>
       <c r="CW11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>441.541</t>
+          <t>357.708</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.88</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5988,22 +5988,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2024-09-24 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,60 +6029,60 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-2.05</v>
+        <v>-1.31</v>
       </c>
       <c r="AV12" t="n">
-        <v>-1.54</v>
+        <v>-2.21</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>62.82000000000001</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>64.48999999999999</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="BA12" t="n">
-        <v>62.67</v>
+        <v>62.81</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-100.23</t>
+          <t>-151.59</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0</v>
+        <v>-0.17</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-89.76</t>
+          <t>-92.19</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>160464262.4626039</t>
+          <t>206888555.6845361</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>27563613.0</t>
+          <t>22233564.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>24466223.4</v>
+        <v>25293638.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>31726650.4</t>
+          <t>30652839.3</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>59736093.42</v>
+        <v>60000457.76</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-7260427</t>
+          <t>-5359200</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-6748509.315777247</t>
+          <t>-6649559.097476214</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-6375606.054256041</t>
+          <t>-6105332.896820534</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>27563613.0</t>
+          <t>22233564.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6253,27 +6253,27 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
+          <t>61.6</t>
+        </is>
+      </c>
+      <c r="CT12" t="inlineStr">
+        <is>
           <t>62.0</t>
-        </is>
-      </c>
-      <c r="CT12" t="inlineStr">
-        <is>
-          <t>62.2</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>262.987</t>
+          <t>441.541</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-22.88</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6475,22 +6475,22 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2024-09-24 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,75 +6501,75 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.89</v>
+        <v>-2.05</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.33</v>
+        <v>-1.54</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>64.42</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>64.64</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>62.53</v>
+        <v>62.67</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>58.99</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-65.89</t>
+          <t>-100.23</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.19</v>
+        <v>-0</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-87.19</t>
+          <t>-89.23</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>160464262.4626039</t>
+          <t>206888555.6845361</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>16615032.0</t>
+          <t>27563613.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>26739145</v>
+        <v>24466223.4</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>31962058.4</t>
+          <t>31726650.4</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>59364555.32</v>
+        <v>59736093.42</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-5222913</t>
+          <t>-7260427</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-6816309.908781102</t>
+          <t>-6748509.315777247</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-7105087.027226195</t>
+          <t>-6375606.054256041</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>16615032.0</t>
+          <t>27563613.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>350.004</t>
+          <t>262.987</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-19.76</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2024-09-24 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -6988,75 +6988,75 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.85</v>
+        <v>-1.89</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.02</v>
+        <v>-0.33</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>64.42</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>64.78</v>
+        <v>64.63</v>
       </c>
       <c r="BA14" t="n">
-        <v>62.38</v>
+        <v>62.53</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>58.99</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-49.25</t>
+          <t>-65.89</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-85.08</t>
+          <t>-86.53</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>160464262.4626039</t>
+          <t>206888555.6845361</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>22286805.0</t>
+          <t>16615032.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>26320663.6</v>
+        <v>26739145</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>32802731.3</t>
+          <t>31962058.4</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>59256422.48</v>
+        <v>59364555.32</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-6482067</t>
+          <t>-5222913</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-6763804.978154721</t>
+          <t>-6816309.908781102</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-6720387.344782621</t>
+          <t>-7105087.027226195</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>22286805.0</t>
+          <t>16615032.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7227,27 +7227,27 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
+          <t>62.7</t>
+        </is>
+      </c>
+      <c r="CT14" t="inlineStr">
+        <is>
           <t>63.2</t>
-        </is>
-      </c>
-      <c r="CT14" t="inlineStr">
-        <is>
-          <t>63.6</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>591.644</t>
+          <t>350.004</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-15.13</t>
+          <t>-19.76</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,146 +7404,146 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2025/09/09</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2024-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>10.53</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2025/09/09</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>2025-11-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>17.80</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>-3.96</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-3.01</v>
+        <v>-1.85</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.22</v>
+        <v>0.02</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>65.06</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>64.91</v>
+        <v>64.78</v>
       </c>
       <c r="BA15" t="n">
-        <v>62.2</v>
+        <v>62.38</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>58.86</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-36.66</t>
+          <t>-49.25</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-83.24</t>
+          <t>-84.31</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>160464262.4626039</t>
+          <t>206888555.6845361</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>37769180.0</t>
+          <t>22286805.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>28801398.4</v>
+        <v>26320663.6</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>33936484.0</t>
+          <t>32802731.3</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>59004025.44</v>
+        <v>59256422.48</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-5135085</t>
+          <t>-6482067</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-6771699.093313283</t>
+          <t>-6763804.978154721</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-6538492.500406712</t>
+          <t>-6720387.344782621</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>37769180.0</t>
+          <t>22286805.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7714,27 +7714,27 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>274.854</t>
+          <t>591.644</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>-15.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7936,101 +7936,101 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2024-09-24 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>17.80</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>78.14</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.43</v>
+        <v>-3.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.96</v>
+        <v>0.22</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>65.67999999999999</t>
+          <t>65.06</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>65.05</v>
+        <v>64.91</v>
       </c>
       <c r="BA16" t="n">
-        <v>62.04</v>
+        <v>62.2</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>58.67</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-15.21</t>
+          <t>-36.66</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-81.70</t>
+          <t>-82.38</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>160464262.4626039</t>
+          <t>206888555.6845361</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>18096487.0</t>
+          <t>37769180.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>36012039.8</v>
+        <v>28801398.4</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>33573275.9</t>
+          <t>33936484.0</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>58779733.82</v>
+        <v>59004025.44</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>2438763</t>
+          <t>-5135085</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-6814100.292023569</t>
+          <t>-6771699.093313283</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-7703951.026283741</t>
+          <t>-6538492.500406712</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>18096487.0</t>
+          <t>37769180.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>16.37</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8201,27 +8201,27 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>589.667</t>
+          <t>274.854</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-7.4</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8423,22 +8423,22 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2024-09-24 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>17.74</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,75 +8449,75 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>65.85</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>78.14</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>1.86</v>
+        <v>-0.43</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>65.58000000000001</t>
+          <t>65.67999999999999</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>65.16</v>
+        <v>65.06</v>
       </c>
       <c r="BA17" t="n">
-        <v>61.82</v>
+        <v>62.04</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>58.67</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-15.21</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-81.01</t>
+          <t>-80.76</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>160464262.4626039</t>
+          <t>206888555.6845361</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>38928221.0</t>
+          <t>18096487.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>38987077.4</v>
+        <v>36012039.8</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>38320197.4</t>
+          <t>33573275.9</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>58694542.18</v>
+        <v>58779733.82</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>666880</t>
+          <t>2438763</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-6652309.249430812</t>
+          <t>-6814100.292023569</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-6985962.13374079</t>
+          <t>-7703951.026283741</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>38928221.0</t>
+          <t>18096487.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>16.37</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8633,17 +8633,17 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8688,27 +8688,27 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>223.538</t>
+          <t>589.667</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8910,22 +8910,22 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2024-09-24 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>17.74</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,17 +8936,17 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
@@ -8955,56 +8955,56 @@
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>0.06</v>
+        <v>1.86</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.2</v>
+        <v>0.64</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>65.06</t>
+          <t>65.58000000000001</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>65.19</v>
+        <v>65.16</v>
       </c>
       <c r="BA18" t="n">
-        <v>61.6</v>
+        <v>61.82</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>58.38</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-31.67</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-80.30</t>
+          <t>-80.03</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>160464262.4626039</t>
+          <t>206888555.6845361</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>14522625.0</t>
+          <t>38928221.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>37184971.8</v>
+        <v>38987077.4</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>36600105.3</t>
+          <t>38320197.4</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>58537667.1</v>
+        <v>58694542.18</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>584866</t>
+          <t>666880</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-6591645.088647179</t>
+          <t>-6652309.249430812</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-7942736.56818869</t>
+          <t>-6985962.13374079</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>14522625.0</t>
+          <t>38928221.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9175,27 +9175,27 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>535.032</t>
+          <t>223.538</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9397,22 +9397,22 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2024-09-24 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,75 +9423,75 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>62.86</t>
+          <t>68.57</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>77.14</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.5</v>
+        <v>0.06</v>
       </c>
       <c r="AV19" t="n">
-        <v>-1.12</v>
+        <v>-0.2</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>64.58000000000001</t>
+          <t>65.06</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>65.31</v>
+        <v>65.19</v>
       </c>
       <c r="BA19" t="n">
-        <v>61.4</v>
+        <v>61.6</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>58.38</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-35.05</t>
+          <t>-31.67</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-78.74</t>
+          <t>-79.29</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>160464262.4626039</t>
+          <t>206888555.6845361</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>34690479.0</t>
+          <t>14522625.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>39284799</v>
+        <v>37184971.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>39695552.0</t>
+          <t>36600105.3</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>58539184.74</v>
+        <v>58537667.1</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-410753</t>
+          <t>584866</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-6345992.092366904</t>
+          <t>-6591645.088647179</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-6411002.739964664</t>
+          <t>-7942736.56818869</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>34690479.0</t>
+          <t>14522625.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9662,17 +9662,17 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9704,22 +9704,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【c】;【x】看好</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1114.493</t>
+          <t>4156.239</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>744.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>-24.07</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9764,32 +9764,32 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2025-11-07 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-10-27 00:00:00</t>
+          <t>2025-11-05 00:00:00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2025-10-29 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>778.0</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -9814,22 +9814,22 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -9839,67 +9839,67 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/09/08</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025/07/08</t>
+          <t>2025/04/01</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>430.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/12/29</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>778.0</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>33.53</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,121 +9910,121 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>3.02</v>
+        <v>-3.25</v>
       </c>
       <c r="AV20" t="n">
-        <v>-1.91</v>
+        <v>0.49</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>64.26</t>
+          <t>769.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>65.51000000000001</v>
+        <v>765.25</v>
       </c>
       <c r="BA20" t="n">
-        <v>61.19</v>
+        <v>730.38</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>58.21</t>
+          <t>676.81</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-37.21</t>
+          <t>-27.97</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.63</v>
+        <v>13.18</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>18.3</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>80.59</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-76.88</t>
+          <t>-77.29</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2025/11/07</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>160464262.4626039</t>
+          <t>5556374910.420618</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>73822387.0</t>
+          <t>3118686184.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>39071569.6</v>
+        <v>1763707053.6</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>48213649.3</t>
+          <t>2322733474.2</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>58015072.56</v>
+        <v>3696867295.36</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-9142079</t>
+          <t>-559026420</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-6334171.974621857</t>
+          <t>-178349145.7503165</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-6154688.673217326</t>
+          <t>-482460364.1605325</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>73822387.0</t>
+          <t>3118686184.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10034,32 +10034,32 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>772.0</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/04</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>17.79</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>洋華</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>洋華</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
@@ -10069,117 +10069,117 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
         <is>
-          <t>8.807108087502199</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>56.33331648044222</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>4.677783569058906</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>54.59</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>45.67%</t>
+          <t>41.69%</t>
         </is>
       </c>
       <c r="CK20" t="inlineStr">
         <is>
-          <t>32.78%</t>
+          <t>20.62%</t>
         </is>
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>235015</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
-          <t>電線電纜器材81.50%、觸控面板18.50% (2024年)</t>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
       <c r="CO20" t="inlineStr">
         <is>
-          <t>洋華-光電業-上市</t>
+          <t>華城-電機機械-上市</t>
         </is>
       </c>
       <c r="CP20" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>777.0</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>744.0</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="CV20" t="inlineStr">
         <is>
-          <t>** 觸控面板 - 觸控面板** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造、電網維運、高壓AMI、低壓AMI、能源管理服務、系統整合服務、電力零售業</t>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
       <c r="CW20" t="inlineStr">
@@ -10196,17 +10196,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>511.567</t>
+          <t>1961.707</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,97 +10226,97 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-41.86</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>778.0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>-1.67</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-37.75</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>-1.96</t>
-        </is>
-      </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -10326,67 +10326,67 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2025/09/09</t>
+          <t>2025/09/08</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025/07/08</t>
+          <t>2025/04/01</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>430.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/12/29</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>778.0</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/11/17</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>738.0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-11-14 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,121 +10397,121 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>1.95</v>
+        <v>-1.52</v>
       </c>
       <c r="AV21" t="n">
-        <v>-2.88</v>
+        <v>1.76</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>63.66</t>
+          <t>776.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>65.54000000000001</v>
+        <v>763.35</v>
       </c>
       <c r="BA21" t="n">
-        <v>60.94</v>
+        <v>727.5</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>675.38</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-51.85</t>
+          <t>-15.10</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.53</v>
+        <v>16.62</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.1</v>
+        <v>19.58</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>80.59</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-74.73</t>
+          <t>-75.71</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2025/11/07</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>160464262.4626039</t>
+          <t>5556374910.420618</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>32971675.0</t>
+          <t>1506889155.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>31134512</v>
+        <v>1490327611.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>50016951.0</t>
+          <t>2563239543.1</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>56656631.86</v>
+        <v>3667295552.7</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-18882439</t>
+          <t>-1072911931</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-6366805.302149953</t>
+          <t>-123056196.948459</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-9761419.839534782</t>
+          <t>-604707568.3894181</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>32971675.0</t>
+          <t>1506889155.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10521,32 +10521,32 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>772.0</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/04</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>洋華</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
         <is>
-          <t>洋華</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>光電業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
@@ -10556,27 +10556,27 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
         <is>
-          <t>8.807108087502199</t>
+          <t>17.93840330060069</t>
         </is>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>56.33331648044222</t>
+          <t>13.37012123856452</t>
         </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>4.677783569058906</t>
+          <t>23.64886415022257</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,87 +10586,87 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>54.59</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>45.67%</t>
+          <t>41.69%</t>
         </is>
       </c>
       <c r="CK21" t="inlineStr">
         <is>
-          <t>32.78%</t>
+          <t>20.62%</t>
         </is>
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>81.73</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>235015</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
-          <t>電線電纜器材81.50%、觸控面板18.50% (2024年)</t>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
       <c r="CO21" t="inlineStr">
         <is>
-          <t>洋華-光電業-上市</t>
+          <t>華城-電機機械-上市</t>
         </is>
       </c>
       <c r="CP21" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>764.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="CV21" t="inlineStr">
         <is>
-          <t>** 觸控面板 - 觸控面板** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造、電網維運、高壓AMI、低壓AMI、能源管理服務、系統整合服務、電力零售業</t>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
       <c r="CW21" t="inlineStr">
@@ -10678,7 +10678,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【c】;【x】看好</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.59</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-74.84</t>
+          <t>-74.79</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>4962242392.051247</t>
+          <t>5556374910.420618</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>54.59</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>244175</t>
+          <t>235015</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.59</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-74.32</t>
+          <t>-74.27</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>4962242392.051247</t>
+          <t>5556374910.420618</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>54.59</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>244175</t>
+          <t>235015</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11921,12 +11921,12 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.59</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-74.13</t>
+          <t>-74.07</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>4962242392.051247</t>
+          <t>5556374910.420618</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>54.59</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>244175</t>
+          <t>235015</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.59</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-74.22</t>
+          <t>-74.17</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>4962242392.051247</t>
+          <t>5556374910.420618</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>54.59</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>244175</t>
+          <t>235015</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12661,12 +12661,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.59</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-74.46</t>
+          <t>-74.41</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>4962242392.051247</t>
+          <t>5556374910.420618</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>54.59</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>244175</t>
+          <t>235015</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13382,12 +13382,12 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.59</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-74.87</t>
+          <t>-74.82</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>4962242392.051247</t>
+          <t>5556374910.420618</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>54.59</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>244175</t>
+          <t>235015</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-12-15 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.59</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-75.23</t>
+          <t>-75.18</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>4962242392.051247</t>
+          <t>5556374910.420618</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>56.71</t>
+          <t>54.59</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>244175</t>
+          <t>235015</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14079,1467 +14079,6 @@
         </is>
       </c>
       <c r="CW28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>【b1】</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>4234.201</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>757.0</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>36.22</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>778.0</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>-2.82</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-2.70</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>5.56</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025/05/23</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>479.0</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>-2.6</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>629.0</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>2025/04/01</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>430.0</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>2025/12/29</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>778.0</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>15.10</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>-2.90</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>45.65</t>
-        </is>
-      </c>
-      <c r="AT29" t="inlineStr">
-        <is>
-          <t>63.54</t>
-        </is>
-      </c>
-      <c r="AU29" t="n">
-        <v>-3.67</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>5.36</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>785.8</t>
-        </is>
-      </c>
-      <c r="AZ29" t="n">
-        <v>732.2</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>694.7</v>
-      </c>
-      <c r="BB29" t="inlineStr">
-        <is>
-          <t>659.35</t>
-        </is>
-      </c>
-      <c r="BC29" t="inlineStr">
-        <is>
-          <t>12.98</t>
-        </is>
-      </c>
-      <c r="BD29" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>19.78</v>
-      </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
-        <is>
-          <t>-75.51</t>
-        </is>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="BI29" t="inlineStr">
-        <is>
-          <t>4962242392.051247</t>
-        </is>
-      </c>
-      <c r="BJ29" t="inlineStr">
-        <is>
-          <t>3247216863.0</t>
-        </is>
-      </c>
-      <c r="BK29" t="n">
-        <v>8005417946.4</v>
-      </c>
-      <c r="BL29" t="inlineStr">
-        <is>
-          <t>5876618473.3</t>
-        </is>
-      </c>
-      <c r="BM29" t="n">
-        <v>3539141509.1</v>
-      </c>
-      <c r="BN29" t="inlineStr">
-        <is>
-          <t>2128799473</t>
-        </is>
-      </c>
-      <c r="BO29" t="inlineStr">
-        <is>
-          <t>529053416.1539711</t>
-        </is>
-      </c>
-      <c r="BP29" t="inlineStr">
-        <is>
-          <t>606165271.4831858</t>
-        </is>
-      </c>
-      <c r="BQ29" t="inlineStr">
-        <is>
-          <t>3247216863.0</t>
-        </is>
-      </c>
-      <c r="BR29" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="BS29" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BT29" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BU29" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="BV29" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BW29" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BX29" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BY29" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ29" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="CA29" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="CB29" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="CC29" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="CD29" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="CE29" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="CF29" t="inlineStr">
-        <is>
-          <t>27.29</t>
-        </is>
-      </c>
-      <c r="CG29" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="CH29" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="CI29" t="inlineStr">
-        <is>
-          <t>56.71</t>
-        </is>
-      </c>
-      <c r="CJ29" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="CK29" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="CL29" t="inlineStr">
-        <is>
-          <t>42.28</t>
-        </is>
-      </c>
-      <c r="CM29" t="inlineStr">
-        <is>
-          <t>244175</t>
-        </is>
-      </c>
-      <c r="CN29" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO29" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CP29" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CQ29" t="inlineStr">
-        <is>
-          <t>770.0</t>
-        </is>
-      </c>
-      <c r="CR29" t="inlineStr">
-        <is>
-          <t>782.0</t>
-        </is>
-      </c>
-      <c r="CS29" t="inlineStr">
-        <is>
-          <t>754.0</t>
-        </is>
-      </c>
-      <c r="CT29" t="inlineStr">
-        <is>
-          <t>757.0</t>
-        </is>
-      </c>
-      <c r="CU29" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CV29" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CW29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>【b1】</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>-4.11</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>7082.079</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>765.0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>48.13</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>778.0</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>-1.80</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>5.56</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025/05/23</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>479.0</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>-2.63</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>629.0</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>2025/04/01</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>430.0</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>2025/12/29</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>778.0</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>-5.23</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>54.35</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr">
-        <is>
-          <t>80.01</t>
-        </is>
-      </c>
-      <c r="AU30" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>5.83</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>5.13</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>786.6</t>
-        </is>
-      </c>
-      <c r="AZ30" t="n">
-        <v>731.3</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>691.04</v>
-      </c>
-      <c r="BB30" t="inlineStr">
-        <is>
-          <t>657.35</t>
-        </is>
-      </c>
-      <c r="BC30" t="inlineStr">
-        <is>
-          <t>27.03</t>
-        </is>
-      </c>
-      <c r="BD30" t="n">
-        <v>24.31</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="BF30" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr">
-        <is>
-          <t>-76.30</t>
-        </is>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="BI30" t="inlineStr">
-        <is>
-          <t>4962242392.051247</t>
-        </is>
-      </c>
-      <c r="BJ30" t="inlineStr">
-        <is>
-          <t>5523746873.0</t>
-        </is>
-      </c>
-      <c r="BK30" t="n">
-        <v>8476813250.4</v>
-      </c>
-      <c r="BL30" t="inlineStr">
-        <is>
-          <t>5722498461.3</t>
-        </is>
-      </c>
-      <c r="BM30" t="n">
-        <v>3487026374.8</v>
-      </c>
-      <c r="BN30" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BO30" t="inlineStr">
-        <is>
-          <t>515033078.8213867</t>
-        </is>
-      </c>
-      <c r="BP30" t="inlineStr">
-        <is>
-          <t>985542631.6889648</t>
-        </is>
-      </c>
-      <c r="BQ30" t="inlineStr">
-        <is>
-          <t>5523746873.0</t>
-        </is>
-      </c>
-      <c r="BR30" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="BS30" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BT30" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BU30" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="BV30" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BW30" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BX30" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BY30" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ30" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="CA30" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="CB30" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="CC30" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="CD30" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="CE30" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF30" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
-      </c>
-      <c r="CG30" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="CH30" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="CI30" t="inlineStr">
-        <is>
-          <t>56.71</t>
-        </is>
-      </c>
-      <c r="CJ30" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="CK30" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="CL30" t="inlineStr">
-        <is>
-          <t>42.28</t>
-        </is>
-      </c>
-      <c r="CM30" t="inlineStr">
-        <is>
-          <t>244175</t>
-        </is>
-      </c>
-      <c r="CN30" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO30" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CP30" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CQ30" t="inlineStr">
-        <is>
-          <t>803.0</t>
-        </is>
-      </c>
-      <c r="CR30" t="inlineStr">
-        <is>
-          <t>806.0</t>
-        </is>
-      </c>
-      <c r="CS30" t="inlineStr">
-        <is>
-          <t>764.0</t>
-        </is>
-      </c>
-      <c r="CT30" t="inlineStr">
-        <is>
-          <t>765.0</t>
-        </is>
-      </c>
-      <c r="CU30" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CV30" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CW30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>【b1】</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>10261.373</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>798.0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>68.20</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>778.0</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>5.56</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025/05/23</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>479.0</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>629.0</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>2025/04/01</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>430.0</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>2025/12/29</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>778.0</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>36.59</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>-2.60</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>90.62</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr">
-        <is>
-          <t>95.22</t>
-        </is>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>6.31</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>4.85</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>789.4</t>
-        </is>
-      </c>
-      <c r="AZ31" t="n">
-        <v>730.55</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>687.1799999999999</v>
-      </c>
-      <c r="BB31" t="inlineStr">
-        <is>
-          <t>655.41</t>
-        </is>
-      </c>
-      <c r="BC31" t="inlineStr">
-        <is>
-          <t>43.73</t>
-        </is>
-      </c>
-      <c r="BD31" t="n">
-        <v>25.65</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>17.84</v>
-      </c>
-      <c r="BF31" t="inlineStr">
-        <is>
-          <t>80.75</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
-        <is>
-          <t>-77.90</t>
-        </is>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="BI31" t="inlineStr">
-        <is>
-          <t>4962242392.051247</t>
-        </is>
-      </c>
-      <c r="BJ31" t="inlineStr">
-        <is>
-          <t>8256630442.0</t>
-        </is>
-      </c>
-      <c r="BK31" t="n">
-        <v>8909321018.4</v>
-      </c>
-      <c r="BL31" t="inlineStr">
-        <is>
-          <t>5296907828.0</t>
-        </is>
-      </c>
-      <c r="BM31" t="n">
-        <v>3388298921.02</v>
-      </c>
-      <c r="BN31" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BO31" t="inlineStr">
-        <is>
-          <t>429485887.3909179</t>
-        </is>
-      </c>
-      <c r="BP31" t="inlineStr">
-        <is>
-          <t>1248398408.351187</t>
-        </is>
-      </c>
-      <c r="BQ31" t="inlineStr">
-        <is>
-          <t>8256630442.0</t>
-        </is>
-      </c>
-      <c r="BR31" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="BS31" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BT31" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BU31" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="BV31" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BW31" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BX31" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BY31" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ31" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="CA31" t="inlineStr">
-        <is>
-          <t>17.93840330060069</t>
-        </is>
-      </c>
-      <c r="CB31" t="inlineStr">
-        <is>
-          <t>13.37012123856452</t>
-        </is>
-      </c>
-      <c r="CC31" t="inlineStr">
-        <is>
-          <t>23.64886415022257</t>
-        </is>
-      </c>
-      <c r="CD31" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE31" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF31" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
-      </c>
-      <c r="CG31" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="CH31" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="CI31" t="inlineStr">
-        <is>
-          <t>56.71</t>
-        </is>
-      </c>
-      <c r="CJ31" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="CK31" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="CL31" t="inlineStr">
-        <is>
-          <t>42.28</t>
-        </is>
-      </c>
-      <c r="CM31" t="inlineStr">
-        <is>
-          <t>244175</t>
-        </is>
-      </c>
-      <c r="CN31" t="inlineStr">
-        <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO31" t="inlineStr">
-        <is>
-          <t>華城-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CP31" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CQ31" t="inlineStr">
-        <is>
-          <t>812.0</t>
-        </is>
-      </c>
-      <c r="CR31" t="inlineStr">
-        <is>
-          <t>834.0</t>
-        </is>
-      </c>
-      <c r="CS31" t="inlineStr">
-        <is>
-          <t>783.0</t>
-        </is>
-      </c>
-      <c r="CT31" t="inlineStr">
-        <is>
-          <t>798.0</t>
-        </is>
-      </c>
-      <c r="CU31" t="inlineStr">
-        <is>
-          <t>27.74</t>
-        </is>
-      </c>
-      <c r="CV31" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
-        </is>
-      </c>
-      <c r="CW31" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/電網營造.xlsx
+++ b/Result/checksun_type/電網營造.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1981.693</t>
+          <t>1301.705</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.02</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.6</v>
+        <v>0.73</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.16</v>
+        <v>-0.8</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>95.18</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>96.3</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>100.41</v>
+        <v>100.16</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>102.45</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>14.80</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-1.56</v>
+        <v>-1.41</v>
       </c>
       <c r="BE2" t="n">
-        <v>-1.83</v>
+        <v>-1.74</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-143.33</t>
+          <t>-141.37</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>392326667.2838115</t>
+          <t>391908415.2730061</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>191289865.0</t>
+          <t>125200956.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>224510210.6</v>
+        <v>199507314.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>238204156.4</t>
+          <t>230316177.2</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>186792728.42</v>
+        <v>185297791.34</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-13693945</t>
+          <t>-30808862</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>17197183.38420958</t>
+          <t>15528304.79779835</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>16177768.71269077</t>
+          <t>6349472.572536558</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>191289865.0</t>
+          <t>125200956.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
+          <t>95.6</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
           <t>96.0</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>96.7</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2555.723</t>
+          <t>1981.693</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>95.9</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.79</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>19.49</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>48.33</t>
+          <t>65.45</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.84</v>
+        <v>1.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.51</v>
+        <v>-1.16</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>95.18</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>96.56</v>
+        <v>96.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>100.67</v>
+        <v>100.41</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>102.74</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>14.80</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-1.79</v>
+        <v>-1.56</v>
       </c>
       <c r="BE3" t="n">
-        <v>-1.9</v>
+        <v>-1.83</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-144.93</t>
+          <t>-143.33</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>392326667.2838115</t>
+          <t>391908415.2730061</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>243907241.0</t>
+          <t>191289865.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>319761015.4</v>
+        <v>224510210.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>229621344.7</t>
+          <t>238204156.4</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>186631297.06</v>
+        <v>186792728.42</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>90139670</t>
+          <t>-13693945</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>17382531.50630391</t>
+          <t>17197183.38420958</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>22559459.78031501</t>
+          <t>16177768.71269077</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>243907241.0</t>
+          <t>191289865.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>95.9</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2309.758</t>
+          <t>2555.723</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,149 +1937,149 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>95.9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>39.26</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-7.79</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/09/19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>98.4</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/10/02</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
           <t>93.2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3.62</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>26.60</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>104.5</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-10.38</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4.31</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/09/19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>98.4</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/10/02</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>93.2</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>2025/12/12</t>
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.72</t>
+          <t>25.14</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>48.33</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.69</v>
+        <v>0.84</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.13</v>
+        <v>-1.51</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>96.86</v>
+        <v>96.56</v>
       </c>
       <c r="BA4" t="n">
-        <v>100.92</v>
+        <v>100.67</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>102.88</t>
+          <t>102.74</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-1.97</v>
+        <v>-1.79</v>
       </c>
       <c r="BE4" t="n">
-        <v>-1.92</v>
+        <v>-1.9</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-145.57</t>
+          <t>-144.93</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>392326667.2838115</t>
+          <t>391908415.2730061</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>215963267.0</t>
+          <t>243907241.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>294688723.6</v>
+        <v>319761015.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>232775070.3</t>
+          <t>229621344.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>187712937.84</v>
+        <v>186631297.06</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>61913653</t>
+          <t>90139670</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>16441271.82012008</t>
+          <t>17382531.50630391</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>25232890.3133384</t>
+          <t>22559459.78031501</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>215963267.0</t>
+          <t>243907241.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>95.9</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2329.335</t>
+          <t>2309.758</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.94</t>
+          <t>-10.38</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>22.72</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>65.38</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.04</v>
+        <v>-1.69</v>
       </c>
       <c r="AV5" t="n">
-        <v>-2.69</v>
+        <v>-2.13</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>97.34999999999999</v>
+        <v>96.86</v>
       </c>
       <c r="BA5" t="n">
-        <v>101.26</v>
+        <v>100.92</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>103.02</t>
+          <t>102.88</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-1.91</v>
+        <v>-1.97</v>
       </c>
       <c r="BE5" t="n">
-        <v>-1.91</v>
+        <v>-1.92</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-145.26</t>
+          <t>-145.57</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>392326667.2838115</t>
+          <t>391908415.2730061</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>221175245.0</t>
+          <t>215963267.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>287216689.6</v>
+        <v>294688723.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>222565975.8</t>
+          <t>232775070.3</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>189489206.36</v>
+        <v>187712937.84</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>64650713</t>
+          <t>61913653</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>14842795.73044402</t>
+          <t>16441271.82012008</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>31144899.34932396</t>
+          <t>25232890.3133384</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>221175245.0</t>
+          <t>215963267.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>95.9</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2622.443</t>
+          <t>2329.335</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17.81</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-8.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>25.80</t>
+          <t>22.91</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,63 +3092,63 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>61.67</t>
+          <t>65.38</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.82</v>
+        <v>-0.04</v>
       </c>
       <c r="AV6" t="n">
-        <v>-3.22</v>
+        <v>-2.69</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>94.62</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>97.77</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="BA6" t="n">
-        <v>101.55</v>
+        <v>101.26</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>103.17</t>
+          <t>103.02</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-1.95</v>
+        <v>-1.91</v>
       </c>
       <c r="BE6" t="n">
         <v>-1.91</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-145.27</t>
+          <t>-145.26</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>392326667.2838115</t>
+          <t>391908415.2730061</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>250215435.0</t>
+          <t>221175245.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>261125039.6</v>
+        <v>287216689.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>221655466.3</t>
+          <t>222565975.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>194260067.76</v>
+        <v>189489206.36</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>39469573</t>
+          <t>64650713</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>11878776.89064767</t>
+          <t>14842795.73044402</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>37919882.49539891</t>
+          <t>31144899.34932396</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>250215435.0</t>
+          <t>221175245.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>95.9</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6854.831</t>
+          <t>2622.443</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>17.81</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.40</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>67.43</t>
+          <t>25.80</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>61.67</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.95</v>
+        <v>0.82</v>
       </c>
       <c r="AV7" t="n">
-        <v>-3.76</v>
+        <v>-3.22</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>94.62</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>98.15000000000001</v>
+        <v>97.77</v>
       </c>
       <c r="BA7" t="n">
-        <v>101.78</v>
+        <v>101.55</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>103.3</t>
+          <t>103.17</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-2.04</v>
+        <v>-1.95</v>
       </c>
       <c r="BE7" t="n">
-        <v>-1.9</v>
+        <v>-1.91</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-145.03</t>
+          <t>-145.27</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>392326667.2838115</t>
+          <t>391908415.2730061</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>667543889.0</t>
+          <t>250215435.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>251898102.2</v>
+        <v>261125039.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>210921622.4</t>
+          <t>221655466.3</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>193065355.42</v>
+        <v>194260067.76</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>40976479</t>
+          <t>39469573</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>7144030.417056534</t>
+          <t>11878776.89064767</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>43132699.40067032</t>
+          <t>37919882.49539891</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>667543889.0</t>
+          <t>250215435.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-10.00</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>96.7</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1261.569</t>
+          <t>6854.831</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.23</t>
+          <t>-7.40</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>67.43</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>40.83</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.13</v>
+        <v>1.95</v>
       </c>
       <c r="AV8" t="n">
-        <v>-3.98</v>
+        <v>-3.76</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>94.52000000000001</t>
+          <t>94.46</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>98.44</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>101.97</v>
+        <v>101.78</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>103.3</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-19.62</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-2.23</v>
+        <v>-2.04</v>
       </c>
       <c r="BE8" t="n">
-        <v>-1.86</v>
+        <v>-1.9</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-144.17</t>
+          <t>-145.03</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>392326667.2838115</t>
+          <t>391908415.2730061</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>118545782.0</t>
+          <t>667543889.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>139481674</v>
+        <v>251898102.2</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>154174301.4</t>
+          <t>210921622.4</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>181554361.68</v>
+        <v>193065355.42</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-14692627</t>
+          <t>40976479</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>600636.0563994827</t>
+          <t>7144030.417056534</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>4325364.215319782</t>
+          <t>43132699.40067032</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>118545782.0</t>
+          <t>667543889.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1915.001</t>
+          <t>1261.569</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.67</t>
+          <t>-9.23</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.98</v>
+        <v>-0.13</v>
       </c>
       <c r="AV9" t="n">
-        <v>-4.11</v>
+        <v>-3.98</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>94.78</t>
+          <t>94.52000000000001</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>98.84</v>
+        <v>98.44</v>
       </c>
       <c r="BA9" t="n">
-        <v>102.2</v>
+        <v>101.97</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>103.54</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-26.27</t>
+          <t>-19.62</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-2.24</v>
+        <v>-2.23</v>
       </c>
       <c r="BE9" t="n">
-        <v>-1.77</v>
+        <v>-1.86</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-142.01</t>
+          <t>-144.17</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>392326667.2838115</t>
+          <t>391908415.2730061</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>178603097.0</t>
+          <t>118545782.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>170861417</v>
+        <v>139481674</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>149993947.3</t>
+          <t>154174301.4</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>181112287.28</v>
+        <v>181554361.68</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>20867469</t>
+          <t>-14692627</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-76587.24522239016</t>
+          <t>600636.0563994827</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>7553062.407129079</t>
+          <t>4325364.215319782</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>178603097.0</t>
+          <t>118545782.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>959.354</t>
+          <t>1915.001</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5055,51 +5055,51 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-1.55</v>
+        <v>-1.98</v>
       </c>
       <c r="AV10" t="n">
-        <v>-3.77</v>
+        <v>-4.11</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>95.58</t>
+          <t>94.78</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>99.31999999999999</v>
+        <v>98.84</v>
       </c>
       <c r="BA10" t="n">
-        <v>102.46</v>
+        <v>102.2</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>103.72</t>
+          <t>103.54</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-24.62</t>
+          <t>-26.27</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-2.06</v>
+        <v>-2.24</v>
       </c>
       <c r="BE10" t="n">
-        <v>-1.66</v>
+        <v>-1.77</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-139.25</t>
+          <t>-142.01</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>392326667.2838115</t>
+          <t>391908415.2730061</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>90716995.0</t>
+          <t>178603097.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>157915262</v>
+        <v>170861417</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>141020232.6</t>
+          <t>149993947.3</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>180088637.34</v>
+        <v>181112287.28</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>16895029</t>
+          <t>20867469</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-1463796.272922657</t>
+          <t>-76587.24522239016</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>5459595.273744881</t>
+          <t>7553062.407129079</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>90716995.0</t>
+          <t>178603097.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-12.36</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>477.771</t>
+          <t>927.728</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5532,61 +5532,61 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>928</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>65.18</t>
+          <t>72.76</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>1.86</v>
+        <v>-0.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.32</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>63.52</t>
+          <t>63.77999999999999</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>64.04000000000001</v>
+        <v>63.98</v>
       </c>
       <c r="BA11" t="n">
-        <v>63.47</v>
+        <v>63.64</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-161.21</t>
+          <t>-418.88</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-98.81</t>
+          <t>-99.42</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>205930906.9579918</t>
+          <t>205692432.5337423</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>31117974.0</t>
+          <t>59544609.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>27939157.8</v>
+        <v>35401366.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>26202690.6</t>
+          <t>30347502.8</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>61251944.26</v>
+        <v>62274667.48</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>1736467</t>
+          <t>5053863</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-5464191.371944392</t>
+          <t>-4635977.829801133</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-2628250.995542113</t>
+          <t>-80803.34801320732</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>31117974.0</t>
+          <t>59544609.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5766,27 +5766,27 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>808.164</t>
+          <t>477.771</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>14.37</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6019,61 +6019,61 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>928</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>65.18</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>3.62</v>
+        <v>1.86</v>
       </c>
       <c r="AV12" t="n">
-        <v>-1.53</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>63.02</t>
+          <t>63.52</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>64</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>63.28</v>
+        <v>63.47</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>59.64</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-264.28</t>
+          <t>-161.21</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.11</v>
+        <v>-0.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-98.34</t>
+          <t>-98.81</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>205930906.9579918</t>
+          <t>205692432.5337423</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>52049708.0</t>
+          <t>31117974.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>27228285.6</v>
+        <v>27939157.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>26983715.3</t>
+          <t>26202690.6</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>60899042.52</v>
+        <v>61251944.26</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>244570</t>
+          <t>1736467</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-5979816.894926624</t>
+          <t>-5464191.371944392</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-3127884.920742612</t>
+          <t>-2628250.995542113</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>52049708.0</t>
+          <t>31117974.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.19</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6253,27 +6253,27 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>304.132</t>
+          <t>808.164</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-13.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6506,61 +6506,61 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>928</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0.32</v>
+        <v>3.62</v>
       </c>
       <c r="AV13" t="n">
-        <v>-2.09</v>
+        <v>-1.53</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>63.02</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>63.94</v>
+        <v>64</v>
       </c>
       <c r="BA13" t="n">
-        <v>63.09</v>
+        <v>63.28</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>59.48</t>
+          <t>59.64</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-343.71</t>
+          <t>-264.28</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.28</v>
+        <v>-0.11</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-97.24</t>
+          <t>-98.34</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>205930906.9579918</t>
+          <t>205692432.5337423</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>19054377.0</t>
+          <t>52049708.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>20141350.4</v>
+        <v>27228285.6</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>23231007.0</t>
+          <t>26983715.3</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>60084776.06</v>
+        <v>60899042.52</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-3089656</t>
+          <t>244570</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-6498349.9811419</t>
+          <t>-5979816.894926624</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-5972623.281002525</t>
+          <t>-3127884.920742612</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>19054377.0</t>
+          <t>52049708.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>63.3</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>243.137</t>
+          <t>304.132</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-16.16</t>
+          <t>-13.30</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>928</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7003,51 +7003,51 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.06</v>
+        <v>0.32</v>
       </c>
       <c r="AV14" t="n">
-        <v>-1.89</v>
+        <v>-2.09</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>62.76000000000001</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>63.97</v>
+        <v>63.94</v>
       </c>
       <c r="BA14" t="n">
-        <v>62.96</v>
+        <v>63.09</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>59.36</t>
+          <t>59.48</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-208.68</t>
+          <t>-343.71</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.23</v>
+        <v>-0.28</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-94.87</t>
+          <t>-97.24</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>205930906.9579918</t>
+          <t>205692432.5337423</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>15240166.0</t>
+          <t>19054377.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>20787836</v>
+        <v>20141350.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>24794617.2</t>
+          <t>23231007.0</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>60037749.24</v>
+        <v>60084776.06</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-4006781</t>
+          <t>-3089656</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-6593936.653894514</t>
+          <t>-6498349.9811419</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-6288013.214195162</t>
+          <t>-5972623.281002525</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>15240166.0</t>
+          <t>19054377.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7227,17 +7227,17 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>357.708</t>
+          <t>243.137</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-16.16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7480,61 +7480,61 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>928</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-1.31</v>
+        <v>0.06</v>
       </c>
       <c r="AV15" t="n">
-        <v>-2.21</v>
+        <v>-1.89</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>62.82000000000001</t>
+          <t>62.76000000000001</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>64.23999999999999</v>
+        <v>63.97</v>
       </c>
       <c r="BA15" t="n">
-        <v>62.81</v>
+        <v>62.96</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.36</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-151.59</t>
+          <t>-208.68</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.17</v>
+        <v>-0.23</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-92.19</t>
+          <t>-94.87</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>205930906.9579918</t>
+          <t>205692432.5337423</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>22233564.0</t>
+          <t>15240166.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>25293638.8</v>
+        <v>20787836</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>30652839.3</t>
+          <t>24794617.2</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>60000457.76</v>
+        <v>60037749.24</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-5359200</t>
+          <t>-4006781</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-6649559.097476214</t>
+          <t>-6593936.653894514</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-6105332.896820534</t>
+          <t>-6288013.214195162</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>22233564.0</t>
+          <t>15240166.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7714,27 +7714,27 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>441.541</t>
+          <t>357.708</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-22.88</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>928</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7977,51 +7977,51 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-2.05</v>
+        <v>-1.31</v>
       </c>
       <c r="AV16" t="n">
-        <v>-1.54</v>
+        <v>-2.21</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>62.82000000000001</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>64.48999999999999</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="BA16" t="n">
-        <v>62.67</v>
+        <v>62.81</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-100.23</t>
+          <t>-151.59</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0</v>
+        <v>-0.17</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-89.23</t>
+          <t>-92.19</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>205930906.9579918</t>
+          <t>205692432.5337423</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>27563613.0</t>
+          <t>22233564.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>24466223.4</v>
+        <v>25293638.8</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>31726650.4</t>
+          <t>30652839.3</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>59736093.42</v>
+        <v>60000457.76</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-7260427</t>
+          <t>-5359200</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-6748509.315777247</t>
+          <t>-6649559.097476214</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-6375606.054256041</t>
+          <t>-6105332.896820534</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>27563613.0</t>
+          <t>22233564.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8201,27 +8201,27 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
+          <t>61.6</t>
+        </is>
+      </c>
+      <c r="CT16" t="inlineStr">
+        <is>
           <t>62.0</t>
-        </is>
-      </c>
-      <c r="CT16" t="inlineStr">
-        <is>
-          <t>62.2</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>262.987</t>
+          <t>441.541</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-22.88</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8454,61 +8454,61 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>928</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.89</v>
+        <v>-2.05</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.33</v>
+        <v>-1.54</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>64.42</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>64.63</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="BA17" t="n">
-        <v>62.53</v>
+        <v>62.67</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>58.99</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-65.89</t>
+          <t>-100.23</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.19</v>
+        <v>-0</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-86.53</t>
+          <t>-89.23</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>205930906.9579918</t>
+          <t>205692432.5337423</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>16615032.0</t>
+          <t>27563613.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>26739145</v>
+        <v>24466223.4</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>31962058.4</t>
+          <t>31726650.4</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>59364555.32</v>
+        <v>59736093.42</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-5222913</t>
+          <t>-7260427</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-6816309.908781102</t>
+          <t>-6748509.315777247</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-7105087.027226195</t>
+          <t>-6375606.054256041</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>16615032.0</t>
+          <t>27563613.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>350.004</t>
+          <t>262.987</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-19.76</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8915,12 +8915,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -8941,61 +8941,61 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>928</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-1.85</v>
+        <v>-1.89</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.02</v>
+        <v>-0.33</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>64.42</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>64.78</v>
+        <v>64.63</v>
       </c>
       <c r="BA18" t="n">
-        <v>62.38</v>
+        <v>62.53</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>58.99</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-49.25</t>
+          <t>-65.89</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-84.31</t>
+          <t>-86.53</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>205930906.9579918</t>
+          <t>205692432.5337423</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>22286805.0</t>
+          <t>16615032.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>26320663.6</v>
+        <v>26739145</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>32802731.3</t>
+          <t>31962058.4</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>59256422.48</v>
+        <v>59364555.32</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-6482067</t>
+          <t>-5222913</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-6763804.978154721</t>
+          <t>-6816309.908781102</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-6720387.344782621</t>
+          <t>-7105087.027226195</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>22286805.0</t>
+          <t>16615032.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9175,27 +9175,27 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
+          <t>62.7</t>
+        </is>
+      </c>
+      <c r="CT18" t="inlineStr">
+        <is>
           <t>63.2</t>
-        </is>
-      </c>
-      <c r="CT18" t="inlineStr">
-        <is>
-          <t>63.6</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>591.644</t>
+          <t>350.004</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-15.13</t>
+          <t>-19.76</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,72 +9352,72 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2025/09/09</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2024-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>10.53</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2025/09/09</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2024-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>17.80</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>-3.96</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr"/>
@@ -9428,61 +9428,61 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>928</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-3.01</v>
+        <v>-1.85</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.22</v>
+        <v>0.02</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>65.06</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>64.91</v>
+        <v>64.78</v>
       </c>
       <c r="BA19" t="n">
-        <v>62.2</v>
+        <v>62.38</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>58.86</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-36.66</t>
+          <t>-49.25</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-82.38</t>
+          <t>-84.31</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>205930906.9579918</t>
+          <t>205692432.5337423</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>37769180.0</t>
+          <t>22286805.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>28801398.4</v>
+        <v>26320663.6</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>33936484.0</t>
+          <t>32802731.3</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>59004025.44</v>
+        <v>59256422.48</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-5135085</t>
+          <t>-6482067</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-6771699.093313283</t>
+          <t>-6763804.978154721</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-6538492.500406712</t>
+          <t>-6720387.344782621</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>37769180.0</t>
+          <t>22286805.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.26</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.27</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9662,27 +9662,27 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>光電業右上上市</t>
+          <t>光電業平上市</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3013.515</t>
+          <t>3554.352</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>20.81</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>10.75</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,17 +9910,17 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
@@ -9929,47 +9929,47 @@
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>-2.82</v>
+        <v>-3.63</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>748.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>769.7</v>
+        <v>769.95</v>
       </c>
       <c r="BA20" t="n">
-        <v>739.48</v>
+        <v>741.8200000000001</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>681.3</t>
+          <t>682.69</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-51.63</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>6.3</v>
+        <v>3.96</v>
       </c>
       <c r="BE20" t="n">
-        <v>13.03</v>
+        <v>11.21</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-83.84</t>
+          <t>-86.09</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>5539474058.790983</t>
+          <t>5536225627.680982</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>2248543117.0</t>
+          <t>2633994164.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>2047982952.6</v>
+        <v>2273403954.4</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1978203987.1</t>
+          <t>1881865782.9</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>3757037790.8</v>
+        <v>3732660125.72</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>69778965</t>
+          <t>391538171</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-292442611.4001625</t>
+          <t>-300392586.3125705</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-423054071.5803742</t>
+          <t>-344117448.3308139</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>2248543117.0</t>
+          <t>2633994164.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>26.50</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>232172</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>744.0</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>734.0</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>755.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2698.297</t>
+          <t>3013.515</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-12.26</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>10.75</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.68</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AV21" t="n">
-        <v>-2.1</v>
+        <v>-2.82</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>751.6</t>
+          <t>748.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>767.7</v>
+        <v>769.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>736.22</v>
+        <v>739.48</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>679.62</t>
+          <t>681.3</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-51.33</t>
+          <t>-51.63</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>7.16</v>
+        <v>6.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>14.71</v>
+        <v>13.03</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-81.75</t>
+          <t>-83.84</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>5539474058.790983</t>
+          <t>5536225627.680982</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>2003660242.0</t>
+          <t>2248543117.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>1846894112.8</v>
+        <v>2047982952.6</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>2105065625.8</t>
+          <t>1978203987.1</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>3727166871.58</v>
+        <v>3757037790.8</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-258171513</t>
+          <t>69778965</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-268695073.1855786</t>
+          <t>-292442611.4001625</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-479413275.7733035</t>
+          <t>-423054071.5803742</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>2003660242.0</t>
+          <t>2248543117.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>232172</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>742.0</t>
+          <t>744.0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1835.459</t>
+          <t>2698.297</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-20.88</t>
+          <t>-12.26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="AU22" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
           <t>8.33</t>
         </is>
       </c>
-      <c r="AU22" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>759.4</t>
+          <t>751.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>766.55</v>
+        <v>767.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>733.12</v>
+        <v>736.22</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>678.25</t>
+          <t>679.62</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-41.08</t>
+          <t>-51.33</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>9.779999999999999</v>
+        <v>7.16</v>
       </c>
       <c r="BE22" t="n">
-        <v>16.59</v>
+        <v>14.71</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-79.41</t>
+          <t>-81.75</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>5539474058.790983</t>
+          <t>5536225627.680982</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>1362136065.0</t>
+          <t>2003660242.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>1688682160.8</v>
+        <v>1846894112.8</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>2134225394.4</t>
+          <t>2105065625.8</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>3706118862.84</v>
+        <v>3727166871.58</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-445543233</t>
+          <t>-258171513</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-230382672.7150831</t>
+          <t>-268695073.1855786</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-516567071.0212994</t>
+          <t>-479413275.7733035</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>1362136065.0</t>
+          <t>2003660242.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>232172</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>746.0</t>
+          <t>742.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>752.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>736.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>737.0</t>
+          <t>739.0</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4156.239</t>
+          <t>1835.459</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>744.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-24.07</t>
+          <t>-20.88</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11386,51 +11386,51 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-3.25</v>
+        <v>-2.95</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.49</v>
+        <v>-0.93</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>769.0</t>
+          <t>759.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>765.25</v>
+        <v>766.55</v>
       </c>
       <c r="BA23" t="n">
-        <v>730.38</v>
+        <v>733.12</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>676.81</t>
+          <t>678.25</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-41.08</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>13.18</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BE23" t="n">
-        <v>18.3</v>
+        <v>16.59</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-77.29</t>
+          <t>-79.41</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>5539474058.790983</t>
+          <t>5536225627.680982</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>3118686184.0</t>
+          <t>1362136065.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>1763707053.6</v>
+        <v>1688682160.8</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>2322733474.2</t>
+          <t>2134225394.4</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>3696867295.36</v>
+        <v>3706118862.84</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-559026420</t>
+          <t>-445543233</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-178349145.7503165</t>
+          <t>-230382672.7150831</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-482460364.1605325</t>
+          <t>-516567071.0212994</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>3118686184.0</t>
+          <t>1362136065.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>232172</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>770.0</t>
+          <t>746.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>777.0</t>
+          <t>752.0</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
+          <t>736.0</t>
+        </is>
+      </c>
+      <c r="CT23" t="inlineStr">
+        <is>
           <t>737.0</t>
-        </is>
-      </c>
-      <c r="CT23" t="inlineStr">
-        <is>
-          <t>744.0</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1961.707</t>
+          <t>4156.239</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>744.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-41.86</t>
+          <t>-24.07</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,231 +11858,231 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr">
+      <c r="AU24" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>4.77</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>7.91</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>769.0</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>765.25</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>730.38</v>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>676.81</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>-27.97</t>
+        </is>
+      </c>
+      <c r="BD24" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>80.59</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>-77.29</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>5536225627.680982</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>3118686184.0</t>
+        </is>
+      </c>
+      <c r="BK24" t="n">
+        <v>1763707053.6</v>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>2322733474.2</t>
+        </is>
+      </c>
+      <c r="BM24" t="n">
+        <v>3696867295.36</v>
+      </c>
+      <c r="BN24" t="inlineStr">
+        <is>
+          <t>-559026420</t>
+        </is>
+      </c>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>-178349145.7503165</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>-482460364.1605325</t>
+        </is>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>3118686184.0</t>
+        </is>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
+        <is>
+          <t>772.0</t>
+        </is>
+      </c>
+      <c r="BT24" t="inlineStr">
+        <is>
+          <t>2025/11/04</t>
+        </is>
+      </c>
+      <c r="BU24" t="inlineStr">
+        <is>
+          <t>-3.63</t>
+        </is>
+      </c>
+      <c r="BV24" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BW24" t="inlineStr">
+        <is>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="BX24" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BY24" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ24" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="CA24" t="inlineStr">
+        <is>
+          <t>-11.47675907004918</t>
+        </is>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>17.20625162017854</t>
+        </is>
+      </c>
+      <c r="CC24" t="inlineStr">
+        <is>
+          <t>22.99831432077406</t>
+        </is>
+      </c>
+      <c r="CD24" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE24" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CF24" t="inlineStr">
+        <is>
+          <t>26.82</t>
+        </is>
+      </c>
+      <c r="CG24" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="CH24" t="inlineStr">
+        <is>
+          <t>18.46</t>
+        </is>
+      </c>
+      <c r="CI24" t="inlineStr">
+        <is>
+          <t>53.93</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>41.69%</t>
+        </is>
+      </c>
+      <c r="CK24" t="inlineStr">
+        <is>
+          <t>20.62%</t>
+        </is>
+      </c>
+      <c r="CL24" t="inlineStr">
         <is>
           <t>42.07</t>
         </is>
       </c>
-      <c r="AU24" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>7.72</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>776.8</t>
-        </is>
-      </c>
-      <c r="AZ24" t="n">
-        <v>763.35</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>727.5</v>
-      </c>
-      <c r="BB24" t="inlineStr">
-        <is>
-          <t>675.38</t>
-        </is>
-      </c>
-      <c r="BC24" t="inlineStr">
-        <is>
-          <t>-15.10</t>
-        </is>
-      </c>
-      <c r="BD24" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>19.58</v>
-      </c>
-      <c r="BF24" t="inlineStr">
-        <is>
-          <t>80.59</t>
-        </is>
-      </c>
-      <c r="BG24" t="inlineStr">
-        <is>
-          <t>-75.71</t>
-        </is>
-      </c>
-      <c r="BH24" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="BI24" t="inlineStr">
-        <is>
-          <t>5539474058.790983</t>
-        </is>
-      </c>
-      <c r="BJ24" t="inlineStr">
-        <is>
-          <t>1506889155.0</t>
-        </is>
-      </c>
-      <c r="BK24" t="n">
-        <v>1490327611.4</v>
-      </c>
-      <c r="BL24" t="inlineStr">
-        <is>
-          <t>2563239543.1</t>
-        </is>
-      </c>
-      <c r="BM24" t="n">
-        <v>3667295552.7</v>
-      </c>
-      <c r="BN24" t="inlineStr">
-        <is>
-          <t>-1072911931</t>
-        </is>
-      </c>
-      <c r="BO24" t="inlineStr">
-        <is>
-          <t>-123056196.948459</t>
-        </is>
-      </c>
-      <c r="BP24" t="inlineStr">
-        <is>
-          <t>-604707568.3894181</t>
-        </is>
-      </c>
-      <c r="BQ24" t="inlineStr">
-        <is>
-          <t>1506889155.0</t>
-        </is>
-      </c>
-      <c r="BR24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS24" t="inlineStr">
-        <is>
-          <t>772.0</t>
-        </is>
-      </c>
-      <c r="BT24" t="inlineStr">
-        <is>
-          <t>2025/11/04</t>
-        </is>
-      </c>
-      <c r="BU24" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="BV24" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BW24" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="BX24" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BY24" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ24" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="CA24" t="inlineStr">
-        <is>
-          <t>-11.47675907004918</t>
-        </is>
-      </c>
-      <c r="CB24" t="inlineStr">
-        <is>
-          <t>17.20625162017854</t>
-        </is>
-      </c>
-      <c r="CC24" t="inlineStr">
-        <is>
-          <t>22.99831432077406</t>
-        </is>
-      </c>
-      <c r="CD24" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE24" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF24" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
-      </c>
-      <c r="CG24" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="CH24" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="CI24" t="inlineStr">
-        <is>
-          <t>55.39</t>
-        </is>
-      </c>
-      <c r="CJ24" t="inlineStr">
-        <is>
-          <t>41.69%</t>
-        </is>
-      </c>
-      <c r="CK24" t="inlineStr">
-        <is>
-          <t>20.62%</t>
-        </is>
-      </c>
-      <c r="CL24" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>232172</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>770.0</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>780.0</t>
+          <t>777.0</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>764.0</t>
+          <t>737.0</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>765.0</t>
+          <t>744.0</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1611.151</t>
+          <t>1961.707</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-41.07</t>
+          <t>-41.86</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,29 +12345,29 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>54.48</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-1.1</v>
+        <v>-1.52</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.89</v>
+        <v>1.76</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
@@ -12376,35 +12376,35 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>781.6</t>
+          <t>776.8</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>759.65</v>
+        <v>763.35</v>
       </c>
       <c r="BA25" t="n">
-        <v>723.98</v>
+        <v>727.5</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>673.36</t>
+          <t>675.38</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-8.28</t>
+          <t>-15.10</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>18.64</v>
+        <v>16.62</v>
       </c>
       <c r="BE25" t="n">
-        <v>20.32</v>
+        <v>19.58</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-74.79</t>
+          <t>-75.71</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>5539474058.790983</t>
+          <t>5536225627.680982</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>1243098918.0</t>
+          <t>1506889155.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>1908425021.6</v>
+        <v>1490327611.4</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>3238213671.8</t>
+          <t>2563239543.1</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>3670110650.14</v>
+        <v>3667295552.7</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-1329788650</t>
+          <t>-1072911931</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-35483220.32283011</t>
+          <t>-123056196.948459</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-585057193.8810611</t>
+          <t>-604707568.3894181</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>1243098918.0</t>
+          <t>1506889155.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>232172</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>772.0</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>776.0</t>
+          <t>780.0</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
+          <t>764.0</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>765.0</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>773.0</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1552.526</t>
+          <t>1611.151</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,159 +12651,159 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>773.0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-5.17</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-2.61</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-41.07</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
           <t>778.0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-3.05</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-47.07</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>785.0</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>-0.64</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025/05/23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>479.0</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>2025/12/29</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
         <is>
           <t>778.0</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>5.56</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025/05/23</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>479.0</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>-0.94</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>629.0</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>2025/04/01</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>430.0</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>2025/12/29</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>778.0</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="AK26" t="inlineStr">
         <is>
           <t>2025-12-15 00:00:00</t>
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>51.22</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>55.15</t>
+          <t>54.48</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-0.79</v>
+        <v>-1.1</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.68</v>
+        <v>2.89</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>784.2</t>
+          <t>781.6</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>756.35</v>
+        <v>759.65</v>
       </c>
       <c r="BA26" t="n">
-        <v>720.42</v>
+        <v>723.98</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>671.2</t>
+          <t>673.36</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-8.28</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>20.12</v>
+        <v>18.64</v>
       </c>
       <c r="BE26" t="n">
-        <v>20.74</v>
+        <v>20.32</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-74.27</t>
+          <t>-74.79</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,48 +12910,48 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>5539474058.790983</t>
+          <t>5536225627.680982</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>1212600482.0</t>
+          <t>1243098918.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>2363237138.8</v>
+        <v>1908425021.6</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>4465120110.9</t>
+          <t>3238213671.8</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>3675443180.24</v>
+        <v>3670110650.14</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-2101882972</t>
+          <t>-1329788650</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>64439320.32412098</t>
+          <t>-35483220.32283011</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-507827090.837656</t>
+          <t>-585057193.8810611</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>1212600482.0</t>
+          <t>1243098918.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>232172</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>791.0</t>
+          <t>772.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>791.0</t>
+          <t>776.0</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>776.0</t>
+          <t>765.0</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>778.0</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13113,7 +13113,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2211.011</t>
+          <t>1552.526</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,159 +13138,159 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>778.0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-5.85</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-2.61</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-47.07</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2025-11-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>778.0</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>779.0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>785.0</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-3.97</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>-51.26</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2025-11-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>738.0</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>5.56</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025/05/23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>479.0</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2025/09/08</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2025/04/01</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>430.0</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2025/12/29</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
         <is>
           <t>778.0</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>779.0</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>785.0</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>2025/11/17</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>738.0</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>5.56</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2025/05/23</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>479.0</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2025/09/08</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>629.0</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>2025/04/01</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>430.0</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>2025/12/29</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>778.0</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>2025/11/17</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>738.0</t>
-        </is>
-      </c>
       <c r="AK27" t="inlineStr">
         <is>
           <t>2025-12-15 00:00:00</t>
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>62.22</t>
+          <t>51.22</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>59.41</t>
+          <t>55.15</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>0.54</v>
+        <v>-0.79</v>
       </c>
       <c r="AV27" t="n">
-        <v>3.77</v>
+        <v>3.68</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>780.8</t>
+          <t>784.2</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>752.45</v>
+        <v>756.35</v>
       </c>
       <c r="BA27" t="n">
-        <v>716.76</v>
+        <v>720.42</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>669.24</t>
+          <t>671.2</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>21.21</v>
+        <v>20.12</v>
       </c>
       <c r="BE27" t="n">
-        <v>20.89</v>
+        <v>20.74</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-74.07</t>
+          <t>-74.27</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>5539474058.790983</t>
+          <t>5536225627.680982</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>1737260529.0</t>
+          <t>1212600482.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>2579768628</v>
+        <v>2363237138.8</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>5292593287.2</t>
+          <t>4465120110.9</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>3707101082.28</v>
+        <v>3675443180.24</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2101882972</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>168487758.7171714</t>
+          <t>64439320.32412098</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-376094000.8171616</t>
+          <t>-507827090.837656</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>1737260529.0</t>
+          <t>1212600482.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>28.30</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>232172</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>791.0</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>794.0</t>
+          <t>791.0</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>775.0</t>
+          <t>776.0</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>785.0</t>
+          <t>778.0</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2223.333</t>
+          <t>2211.011</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-49.26</t>
+          <t>-51.26</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>62.22</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>59.41</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>0.54</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>775.2</t>
+          <t>780.8</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>749.65</v>
+        <v>752.45</v>
       </c>
       <c r="BA28" t="n">
-        <v>712.48</v>
+        <v>716.76</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>667.51</t>
+          <t>669.24</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>21.58</v>
+        <v>21.21</v>
       </c>
       <c r="BE28" t="n">
-        <v>20.81</v>
+        <v>20.89</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-74.17</t>
+          <t>-74.07</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,24 +13884,24 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>5539474058.790983</t>
+          <t>5536225627.680982</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>1751788973.0</t>
+          <t>1737260529.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>2881759894.8</v>
+        <v>2579768628</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>5679286572.6</t>
+          <t>5292593287.2</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>3689893009.58</v>
+        <v>3707101082.28</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
@@ -13910,17 +13910,17 @@
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>267502624.0870501</t>
+          <t>168487758.7171714</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-230685520.0801277</t>
+          <t>-376094000.8171616</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>1751788973.0</t>
+          <t>1737260529.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.30</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>42.07</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>232172</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>798.0</t>
+          <t>783.0</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>800.0</t>
+          <t>794.0</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>775.0</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>783.0</t>
+          <t>785.0</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
